--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>September</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> It was tiring but productive day</t>
   </si>
 </sst>
 </file>
@@ -1084,26 +1087,50 @@
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="15" t="str">
+      <c r="A8" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B8" s="14">
+        <v>460</v>
+      </c>
+      <c r="C8" s="14">
+        <v>50</v>
+      </c>
+      <c r="D8" s="14">
+        <v>130</v>
+      </c>
+      <c r="E8" s="14">
+        <v>60</v>
+      </c>
+      <c r="F8" s="14">
+        <v>420</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>50</v>
+      </c>
+      <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J8" s="15" t="str">
+        <v>1170</v>
+      </c>
+      <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="17"/>
+        <v>270</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -217,6 +217,12 @@
   </si>
   <si>
     <t xml:space="preserve"> It was tiring but productive day</t>
+  </si>
+  <si>
+    <t>low</t>
+  </si>
+  <si>
+    <t>It was okay</t>
   </si>
 </sst>
 </file>
@@ -1133,26 +1139,50 @@
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="15" t="str">
+      <c r="A9" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B9" s="14">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14">
+        <v>120</v>
+      </c>
+      <c r="E9" s="14">
+        <v>50</v>
+      </c>
+      <c r="F9" s="14">
+        <v>360</v>
+      </c>
+      <c r="G9" s="14">
+        <v>6</v>
+      </c>
+      <c r="H9" s="14">
+        <v>60</v>
+      </c>
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J9" s="15" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" s="16"/>
-      <c r="N9" s="17"/>
+        <v>340</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1140,7 +1140,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
-        <v>46289</v>
+        <v>46288</v>
       </c>
       <c r="B9" s="14">
         <v>450</v>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -223,6 +223,9 @@
   </si>
   <si>
     <t>It was okay</t>
+  </si>
+  <si>
+    <t>Peaceful day</t>
   </si>
 </sst>
 </file>
@@ -1185,26 +1188,50 @@
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13"/>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15" t="str">
+      <c r="A10" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B10" s="14">
+        <v>460</v>
+      </c>
+      <c r="C10" s="14">
+        <v>30</v>
+      </c>
+      <c r="D10" s="14">
+        <v>150</v>
+      </c>
+      <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>0</v>
+      </c>
+      <c r="G10" s="14">
+        <v>0</v>
+      </c>
+      <c r="H10" s="14">
+        <v>60</v>
+      </c>
+      <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J10" s="15" t="str">
+        <v>750</v>
+      </c>
+      <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" s="16"/>
-      <c r="N10" s="17"/>
+        <v>690</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -226,6 +226,12 @@
   </si>
   <si>
     <t>Peaceful day</t>
+  </si>
+  <si>
+    <t>good</t>
+  </si>
+  <si>
+    <t>Day went fine</t>
   </si>
 </sst>
 </file>
@@ -1234,26 +1240,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B11" s="14">
+        <v>460</v>
+      </c>
+      <c r="C11" s="14">
+        <v>60</v>
+      </c>
+      <c r="D11" s="14">
+        <v>150</v>
+      </c>
+      <c r="E11" s="14">
+        <v>60</v>
+      </c>
+      <c r="F11" s="14">
+        <v>300</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -232,6 +232,9 @@
   </si>
   <si>
     <t>Day went fine</t>
+  </si>
+  <si>
+    <t>it was okay</t>
   </si>
 </sst>
 </file>
@@ -1286,26 +1289,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B12" s="14">
+        <v>450</v>
+      </c>
+      <c r="C12" s="14">
+        <v>60</v>
+      </c>
+      <c r="D12" s="14">
+        <v>200</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
+        <v>180</v>
+      </c>
+      <c r="G12" s="14">
+        <v>3</v>
+      </c>
+      <c r="H12" s="14">
+        <v>60</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>430</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -235,6 +235,9 @@
   </si>
   <si>
     <t>it was okay</t>
+  </si>
+  <si>
+    <t>Today was simple and quiet</t>
   </si>
 </sst>
 </file>
@@ -1335,26 +1338,48 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
+      <c r="A13" s="13">
+        <v>46292</v>
+      </c>
       <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="C13" s="14">
+        <v>60</v>
+      </c>
+      <c r="D13" s="14">
+        <v>200</v>
+      </c>
+      <c r="E13" s="14">
+        <v>70</v>
+      </c>
+      <c r="F13" s="14">
+        <v>0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>0</v>
+      </c>
+      <c r="H13" s="14">
+        <v>60</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>390</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>1050</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>Today was simple and quiet</t>
+  </si>
+  <si>
+    <t>It was just an average day</t>
   </si>
 </sst>
 </file>
@@ -1382,26 +1385,48 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
+      <c r="A14" s="13">
+        <v>46293</v>
+      </c>
       <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="C14" s="14">
+        <v>60</v>
+      </c>
+      <c r="D14" s="14">
+        <v>200</v>
+      </c>
+      <c r="E14" s="14">
+        <v>60</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
+        <v>60</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>380</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>1060</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N14" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -241,6 +241,9 @@
   </si>
   <si>
     <t>It was just an average day</t>
+  </si>
+  <si>
+    <t>The day was calm and okayish</t>
   </si>
 </sst>
 </file>
@@ -1429,26 +1432,48 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
+      <c r="A15" s="13">
+        <v>46294</v>
+      </c>
       <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="C15" s="14">
+        <v>60</v>
+      </c>
+      <c r="D15" s="14">
+        <v>250</v>
+      </c>
+      <c r="E15" s="14">
+        <v>60</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>80</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>450</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>990</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N15" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,9 @@
   </si>
   <si>
     <t>The day was calm and okayish</t>
+  </si>
+  <si>
+    <t>It was a refreshing day</t>
   </si>
 </sst>
 </file>
@@ -1476,26 +1479,48 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
+      <c r="A16" s="13">
+        <v>46295</v>
+      </c>
       <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="C16" s="14">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14">
+        <v>250</v>
+      </c>
+      <c r="E16" s="14">
+        <v>70</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>60</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>440</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>1000</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>It was a refreshing day</t>
+  </si>
+  <si>
+    <t>It was great day</t>
   </si>
 </sst>
 </file>
@@ -1523,26 +1526,48 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
+      <c r="A17" s="13">
+        <v>46296</v>
+      </c>
       <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="C17" s="14">
+        <v>70</v>
+      </c>
+      <c r="D17" s="14">
+        <v>300</v>
+      </c>
+      <c r="E17" s="14">
+        <v>80</v>
+      </c>
+      <c r="F17" s="14">
+        <v>0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>0</v>
+      </c>
+      <c r="H17" s="14">
+        <v>80</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>530</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>910</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -251,6 +251,12 @@
   <si>
     <t>It was great day</t>
   </si>
+  <si>
+    <t>it was busy day</t>
+  </si>
+  <si>
+    <t>Today was little hectic</t>
+  </si>
 </sst>
 </file>
 
@@ -436,7 +442,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -899,7 +927,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N396"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1027,7 +1055,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="42.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8">
         <v>46223</v>
       </c>
@@ -1053,11 +1081,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I64" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J64" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1075,39 +1103,39 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="B7" s="14">
-        <v>450</v>
+        <v>400</v>
       </c>
       <c r="C7" s="14">
         <v>60</v>
       </c>
       <c r="D7" s="14">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="E7" s="14">
         <v>60</v>
       </c>
       <c r="F7" s="14">
-        <v>240</v>
+        <v>420</v>
       </c>
       <c r="G7" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H7" s="14">
         <v>60</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1130</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>310</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="L7" s="16" t="s">
         <v>56</v>
@@ -1116,87 +1144,87 @@
         <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="B8" s="14">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="C8" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D8" s="14">
-        <v>130</v>
+        <v>170</v>
       </c>
       <c r="E8" s="14">
+        <v>70</v>
+      </c>
+      <c r="F8" s="14">
+        <v>360</v>
+      </c>
+      <c r="G8" s="14">
+        <v>6</v>
+      </c>
+      <c r="H8" s="14">
         <v>60</v>
-      </c>
-      <c r="F8" s="14">
-        <v>420</v>
-      </c>
-      <c r="G8" s="14">
-        <v>7</v>
-      </c>
-      <c r="H8" s="14">
-        <v>50</v>
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1150</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="N8" s="17" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
-        <v>46288</v>
+        <v>46282</v>
       </c>
       <c r="B9" s="14">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C9" s="14">
         <v>60</v>
       </c>
       <c r="D9" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E9" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F9" s="14">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="G9" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H9" s="14">
         <v>60</v>
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>1020</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>420</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>55</v>
@@ -1205,44 +1233,44 @@
         <v>55</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="N9" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
-        <v>46289</v>
+        <v>46283</v>
       </c>
       <c r="B10" s="14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C10" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D10" s="14">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E10" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F10" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G10" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H10" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>750</v>
+        <v>1200</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>690</v>
+        <v>240</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>55</v>
@@ -1254,41 +1282,41 @@
         <v>57</v>
       </c>
       <c r="N10" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
-        <v>46290</v>
+        <v>46284</v>
       </c>
       <c r="B11" s="14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C11" s="14">
         <v>60</v>
       </c>
       <c r="D11" s="14">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E11" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F11" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G11" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H11" s="14">
         <v>60</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>890</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>65</v>
@@ -1300,41 +1328,41 @@
         <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="B12" s="14">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C12" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D12" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E12" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F12" s="14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>990</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>65</v>
@@ -1346,154 +1374,162 @@
         <v>57</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
-        <v>46292</v>
-      </c>
-      <c r="B13" s="14"/>
+        <v>46286</v>
+      </c>
+      <c r="B13" s="14">
+        <v>450</v>
+      </c>
       <c r="C13" s="14">
         <v>60</v>
       </c>
       <c r="D13" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E13" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F13" s="14">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G13" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H13" s="14">
         <v>60</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" si="0"/>
-        <v>390</v>
+        <f t="shared" ref="I13:I23" si="2">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
+        <v>1140</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" si="1"/>
-        <v>1050</v>
+        <f t="shared" ref="J13:J23" si="3">IF(I13="","",1440-I13)</f>
+        <v>300</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B14" s="14"/>
+        <v>46287</v>
+      </c>
+      <c r="B14" s="14">
+        <v>460</v>
+      </c>
       <c r="C14" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D14" s="14">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="E14" s="14">
         <v>60</v>
       </c>
       <c r="F14" s="14">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="G14" s="14">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H14" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I14" s="15">
-        <f t="shared" si="0"/>
-        <v>380</v>
+        <f t="shared" si="2"/>
+        <v>1170</v>
       </c>
       <c r="J14" s="15">
-        <f t="shared" si="1"/>
-        <v>1060</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M14" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N14" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
-        <v>46294</v>
-      </c>
-      <c r="B15" s="14"/>
+        <v>46288</v>
+      </c>
+      <c r="B15" s="14">
+        <v>450</v>
+      </c>
       <c r="C15" s="14">
         <v>60</v>
       </c>
       <c r="D15" s="14">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E15" s="14">
+        <v>50</v>
+      </c>
+      <c r="F15" s="14">
+        <v>360</v>
+      </c>
+      <c r="G15" s="14">
+        <v>6</v>
+      </c>
+      <c r="H15" s="14">
         <v>60</v>
       </c>
-      <c r="F15" s="14">
-        <v>0</v>
-      </c>
-      <c r="G15" s="14">
-        <v>0</v>
-      </c>
-      <c r="H15" s="14">
-        <v>80</v>
-      </c>
       <c r="I15" s="15">
-        <f t="shared" si="0"/>
-        <v>450</v>
+        <f t="shared" si="2"/>
+        <v>1100</v>
       </c>
       <c r="J15" s="15">
-        <f t="shared" si="1"/>
-        <v>990</v>
+        <f t="shared" si="3"/>
+        <v>340</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N15" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
-        <v>46295</v>
-      </c>
-      <c r="B16" s="14"/>
+        <v>46289</v>
+      </c>
+      <c r="B16" s="14">
+        <v>460</v>
+      </c>
       <c r="C16" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D16" s="14">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E16" s="14">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
         <v>0</v>
@@ -1505,15 +1541,15 @@
         <v>60</v>
       </c>
       <c r="I16" s="15">
-        <f t="shared" si="0"/>
-        <v>440</v>
+        <f t="shared" si="2"/>
+        <v>750</v>
       </c>
       <c r="J16" s="15">
-        <f t="shared" si="1"/>
-        <v>1000</v>
+        <f t="shared" si="3"/>
+        <v>690</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L16" s="16" t="s">
         <v>56</v>
@@ -1522,39 +1558,41 @@
         <v>57</v>
       </c>
       <c r="N16" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
-        <v>46296</v>
-      </c>
-      <c r="B17" s="14"/>
+        <v>46290</v>
+      </c>
+      <c r="B17" s="14">
+        <v>460</v>
+      </c>
       <c r="C17" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D17" s="14">
+        <v>150</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
         <v>300</v>
       </c>
-      <c r="E17" s="14">
-        <v>80</v>
-      </c>
-      <c r="F17" s="14">
-        <v>0</v>
-      </c>
       <c r="G17" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I17" s="15">
-        <f t="shared" si="0"/>
-        <v>530</v>
+        <f t="shared" si="2"/>
+        <v>1090</v>
       </c>
       <c r="J17" s="15">
-        <f t="shared" si="1"/>
-        <v>910</v>
+        <f t="shared" si="3"/>
+        <v>350</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>65</v>
@@ -1565,141 +1603,285 @@
       <c r="M17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B18" s="14">
+        <v>450</v>
+      </c>
+      <c r="C18" s="14">
+        <v>60</v>
+      </c>
+      <c r="D18" s="14">
+        <v>200</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>180</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3</v>
+      </c>
+      <c r="H18" s="14">
+        <v>60</v>
+      </c>
+      <c r="I18" s="15">
+        <f t="shared" si="2"/>
+        <v>1010</v>
+      </c>
+      <c r="J18" s="15">
+        <f t="shared" si="3"/>
+        <v>430</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B19" s="14">
+        <v>450</v>
+      </c>
+      <c r="C19" s="14">
+        <v>60</v>
+      </c>
+      <c r="D19" s="14">
+        <v>200</v>
+      </c>
+      <c r="E19" s="14">
+        <v>70</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
+        <v>60</v>
+      </c>
+      <c r="I19" s="15">
+        <f t="shared" si="2"/>
+        <v>840</v>
+      </c>
+      <c r="J19" s="15">
+        <f t="shared" si="3"/>
+        <v>600</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B20" s="14">
+        <v>450</v>
+      </c>
+      <c r="C20" s="14">
+        <v>60</v>
+      </c>
+      <c r="D20" s="14">
+        <v>200</v>
+      </c>
+      <c r="E20" s="14">
+        <v>60</v>
+      </c>
+      <c r="F20" s="14">
+        <v>0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>0</v>
+      </c>
+      <c r="H20" s="14">
+        <v>60</v>
+      </c>
+      <c r="I20" s="15">
+        <f t="shared" si="2"/>
+        <v>830</v>
+      </c>
+      <c r="J20" s="15">
+        <f t="shared" si="3"/>
+        <v>610</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N20" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B21" s="14">
+        <v>420</v>
+      </c>
+      <c r="C21" s="14">
+        <v>60</v>
+      </c>
+      <c r="D21" s="14">
+        <v>250</v>
+      </c>
+      <c r="E21" s="14">
+        <v>60</v>
+      </c>
+      <c r="F21" s="14">
+        <v>0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>0</v>
+      </c>
+      <c r="H21" s="14">
+        <v>80</v>
+      </c>
+      <c r="I21" s="15">
+        <f t="shared" si="2"/>
+        <v>870</v>
+      </c>
+      <c r="J21" s="15">
+        <f t="shared" si="3"/>
+        <v>570</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B22" s="14">
+        <v>420</v>
+      </c>
+      <c r="C22" s="14">
+        <v>60</v>
+      </c>
+      <c r="D22" s="14">
+        <v>250</v>
+      </c>
+      <c r="E22" s="14">
+        <v>70</v>
+      </c>
+      <c r="F22" s="14">
+        <v>0</v>
+      </c>
+      <c r="G22" s="14">
+        <v>0</v>
+      </c>
+      <c r="H22" s="14">
+        <v>60</v>
+      </c>
+      <c r="I22" s="15">
+        <f t="shared" si="2"/>
+        <v>860</v>
+      </c>
+      <c r="J22" s="15">
+        <f t="shared" si="3"/>
+        <v>580</v>
+      </c>
+      <c r="K22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L22" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B23" s="14">
+        <v>460</v>
+      </c>
+      <c r="C23" s="14">
+        <v>70</v>
+      </c>
+      <c r="D23" s="14">
+        <v>300</v>
+      </c>
+      <c r="E23" s="14">
+        <v>80</v>
+      </c>
+      <c r="F23" s="14">
+        <v>0</v>
+      </c>
+      <c r="G23" s="14">
+        <v>0</v>
+      </c>
+      <c r="H23" s="14">
+        <v>80</v>
+      </c>
+      <c r="I23" s="15">
+        <f t="shared" si="2"/>
+        <v>990</v>
+      </c>
+      <c r="J23" s="15">
+        <f t="shared" si="3"/>
+        <v>450</v>
+      </c>
+      <c r="K23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L23" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M23" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N23" s="17" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
@@ -2613,11 +2795,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I65:I128" si="4">IF(SUM(B65:F65,H65)=0,"",SUM(B65:F65,H65))</f>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J65:J128" si="5">IF(I65="","",1440-I65)</f>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -2635,11 +2817,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -2657,11 +2839,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -2679,11 +2861,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -2701,11 +2883,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -2723,11 +2905,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -2745,11 +2927,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -2767,11 +2949,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -2789,11 +2971,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -2811,11 +2993,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -2833,11 +3015,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -2855,11 +3037,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -2877,11 +3059,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -2899,11 +3081,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -2921,11 +3103,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -2943,11 +3125,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -2965,11 +3147,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -2987,11 +3169,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3009,11 +3191,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3031,11 +3213,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3053,11 +3235,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3075,11 +3257,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3097,11 +3279,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3119,11 +3301,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3141,11 +3323,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3163,11 +3345,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3185,11 +3367,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3207,11 +3389,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3229,11 +3411,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3251,11 +3433,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3273,11 +3455,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3295,11 +3477,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3317,11 +3499,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3339,11 +3521,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3361,11 +3543,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3383,11 +3565,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3405,11 +3587,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3427,11 +3609,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3449,11 +3631,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3471,11 +3653,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3493,11 +3675,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3515,11 +3697,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3537,11 +3719,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3559,11 +3741,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3581,11 +3763,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3603,11 +3785,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3625,11 +3807,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3647,11 +3829,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3669,11 +3851,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3691,11 +3873,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3713,11 +3895,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -3735,11 +3917,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -3757,11 +3939,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -3779,11 +3961,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -3801,11 +3983,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -3823,11 +4005,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -3845,11 +4027,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -3867,11 +4049,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -3889,11 +4071,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -3911,11 +4093,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -3933,11 +4115,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -3955,11 +4137,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -3977,11 +4159,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -3999,11 +4181,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4021,11 +4203,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I129:I192" si="6">IF(SUM(B129:F129,H129)=0,"",SUM(B129:F129,H129))</f>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J129:J192" si="7">IF(I129="","",1440-I129)</f>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4043,11 +4225,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4065,11 +4247,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4087,11 +4269,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4109,11 +4291,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4131,11 +4313,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4153,11 +4335,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4175,11 +4357,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4197,11 +4379,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4219,11 +4401,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4241,11 +4423,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4263,11 +4445,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4285,11 +4467,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4307,11 +4489,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4329,11 +4511,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4351,11 +4533,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4373,11 +4555,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4395,11 +4577,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4417,11 +4599,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4439,11 +4621,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4461,11 +4643,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4483,11 +4665,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4505,11 +4687,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4527,11 +4709,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4549,11 +4731,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4571,11 +4753,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4593,11 +4775,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4615,11 +4797,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4637,11 +4819,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4659,11 +4841,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4681,11 +4863,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4703,11 +4885,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -4725,11 +4907,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -4747,11 +4929,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -4769,11 +4951,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -4791,11 +4973,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -4813,11 +4995,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -4835,11 +5017,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -4857,11 +5039,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -4879,11 +5061,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -4901,11 +5083,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -4923,11 +5105,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -4945,11 +5127,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -4967,11 +5149,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -4989,11 +5171,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5011,11 +5193,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5033,11 +5215,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5055,11 +5237,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5077,11 +5259,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5099,11 +5281,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5121,11 +5303,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5143,11 +5325,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5165,11 +5347,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5187,11 +5369,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5209,11 +5391,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5231,11 +5413,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5253,11 +5435,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5275,11 +5457,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5297,11 +5479,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5319,11 +5501,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5341,11 +5523,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5363,11 +5545,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5385,11 +5567,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5407,11 +5589,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5429,11 +5611,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I193:I256" si="8">IF(SUM(B193:F193,H193)=0,"",SUM(B193:F193,H193))</f>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J193:J256" si="9">IF(I193="","",1440-I193)</f>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5451,11 +5633,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5473,11 +5655,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5495,11 +5677,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5517,11 +5699,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5539,11 +5721,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5561,11 +5743,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5583,11 +5765,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5605,11 +5787,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5627,11 +5809,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5649,11 +5831,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5671,11 +5853,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5693,11 +5875,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -5715,11 +5897,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -5737,11 +5919,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -5759,11 +5941,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -5781,11 +5963,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -5803,11 +5985,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -5825,11 +6007,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -5847,11 +6029,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -5869,11 +6051,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -5891,11 +6073,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -5913,11 +6095,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -5935,11 +6117,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -5957,11 +6139,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -5979,11 +6161,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6001,11 +6183,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6023,11 +6205,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6045,11 +6227,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6067,11 +6249,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6089,11 +6271,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6111,11 +6293,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6133,11 +6315,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6155,11 +6337,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6177,11 +6359,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6199,11 +6381,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6221,11 +6403,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6243,11 +6425,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6265,11 +6447,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6287,11 +6469,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6309,11 +6491,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6331,11 +6513,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6353,11 +6535,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6375,11 +6557,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6397,11 +6579,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6419,11 +6601,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6441,11 +6623,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6463,11 +6645,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6485,11 +6667,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6507,11 +6689,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6529,11 +6711,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6551,11 +6733,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6573,11 +6755,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6595,11 +6777,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6617,11 +6799,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6639,11 +6821,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6661,11 +6843,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6683,11 +6865,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6705,11 +6887,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -6727,11 +6909,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6749,11 +6931,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6771,11 +6953,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6793,11 +6975,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6815,11 +6997,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6837,11 +7019,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I257:I320" si="10">IF(SUM(B257:F257,H257)=0,"",SUM(B257:F257,H257))</f>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J257:J320" si="11">IF(I257="","",1440-I257)</f>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -6859,11 +7041,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -6881,11 +7063,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -6903,11 +7085,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -6925,11 +7107,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -6947,11 +7129,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -6969,11 +7151,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -6991,11 +7173,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7013,11 +7195,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7035,11 +7217,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7057,11 +7239,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7079,11 +7261,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7101,11 +7283,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7123,11 +7305,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7145,11 +7327,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7167,11 +7349,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7189,11 +7371,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7211,11 +7393,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7233,11 +7415,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7255,11 +7437,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7277,11 +7459,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7299,11 +7481,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7321,11 +7503,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7343,11 +7525,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7365,11 +7547,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7387,11 +7569,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7409,11 +7591,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7431,11 +7613,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7453,11 +7635,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7475,11 +7657,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7497,11 +7679,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7519,11 +7701,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7541,11 +7723,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7563,11 +7745,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7585,11 +7767,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7607,11 +7789,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7629,11 +7811,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7651,11 +7833,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7673,11 +7855,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7695,11 +7877,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -7717,11 +7899,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -7739,11 +7921,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -7761,11 +7943,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -7783,11 +7965,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -7805,11 +7987,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -7827,11 +8009,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -7849,11 +8031,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -7871,11 +8053,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -7893,11 +8075,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -7915,11 +8097,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -7937,11 +8119,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -7959,11 +8141,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -7981,11 +8163,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8003,11 +8185,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8025,11 +8207,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8047,11 +8229,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8069,11 +8251,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8091,11 +8273,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8113,11 +8295,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8135,11 +8317,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8157,11 +8339,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8179,11 +8361,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8201,11 +8383,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8223,11 +8405,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8245,11 +8427,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I321:I384" si="12">IF(SUM(B321:F321,H321)=0,"",SUM(B321:F321,H321))</f>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J321:J384" si="13">IF(I321="","",1440-I321)</f>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -8267,11 +8449,11 @@
       <c r="G322" s="14"/>
       <c r="H322" s="14"/>
       <c r="I322" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J322" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K322" s="16"/>
@@ -8289,11 +8471,11 @@
       <c r="G323" s="14"/>
       <c r="H323" s="14"/>
       <c r="I323" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J323" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K323" s="16"/>
@@ -8311,11 +8493,11 @@
       <c r="G324" s="14"/>
       <c r="H324" s="14"/>
       <c r="I324" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J324" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K324" s="16"/>
@@ -8333,11 +8515,11 @@
       <c r="G325" s="14"/>
       <c r="H325" s="14"/>
       <c r="I325" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J325" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K325" s="16"/>
@@ -8355,11 +8537,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8377,11 +8559,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8399,11 +8581,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8421,11 +8603,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8443,11 +8625,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -8465,11 +8647,11 @@
       <c r="G331" s="14"/>
       <c r="H331" s="14"/>
       <c r="I331" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J331" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K331" s="16"/>
@@ -8487,11 +8669,11 @@
       <c r="G332" s="14"/>
       <c r="H332" s="14"/>
       <c r="I332" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J332" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K332" s="16"/>
@@ -8509,11 +8691,11 @@
       <c r="G333" s="14"/>
       <c r="H333" s="14"/>
       <c r="I333" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J333" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K333" s="16"/>
@@ -8531,11 +8713,11 @@
       <c r="G334" s="14"/>
       <c r="H334" s="14"/>
       <c r="I334" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J334" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K334" s="16"/>
@@ -8553,11 +8735,11 @@
       <c r="G335" s="14"/>
       <c r="H335" s="14"/>
       <c r="I335" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J335" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K335" s="16"/>
@@ -8575,11 +8757,11 @@
       <c r="G336" s="14"/>
       <c r="H336" s="14"/>
       <c r="I336" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J336" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K336" s="16"/>
@@ -8597,11 +8779,11 @@
       <c r="G337" s="14"/>
       <c r="H337" s="14"/>
       <c r="I337" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J337" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K337" s="16"/>
@@ -8619,11 +8801,11 @@
       <c r="G338" s="14"/>
       <c r="H338" s="14"/>
       <c r="I338" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J338" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K338" s="16"/>
@@ -8641,11 +8823,11 @@
       <c r="G339" s="14"/>
       <c r="H339" s="14"/>
       <c r="I339" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J339" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K339" s="16"/>
@@ -8663,11 +8845,11 @@
       <c r="G340" s="14"/>
       <c r="H340" s="14"/>
       <c r="I340" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J340" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K340" s="16"/>
@@ -8685,11 +8867,11 @@
       <c r="G341" s="14"/>
       <c r="H341" s="14"/>
       <c r="I341" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J341" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K341" s="16"/>
@@ -8707,11 +8889,11 @@
       <c r="G342" s="14"/>
       <c r="H342" s="14"/>
       <c r="I342" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J342" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K342" s="16"/>
@@ -8729,11 +8911,11 @@
       <c r="G343" s="14"/>
       <c r="H343" s="14"/>
       <c r="I343" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J343" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K343" s="16"/>
@@ -8751,11 +8933,11 @@
       <c r="G344" s="14"/>
       <c r="H344" s="14"/>
       <c r="I344" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J344" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K344" s="16"/>
@@ -8773,11 +8955,11 @@
       <c r="G345" s="14"/>
       <c r="H345" s="14"/>
       <c r="I345" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J345" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K345" s="16"/>
@@ -8795,11 +8977,11 @@
       <c r="G346" s="14"/>
       <c r="H346" s="14"/>
       <c r="I346" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J346" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K346" s="16"/>
@@ -8817,11 +8999,11 @@
       <c r="G347" s="14"/>
       <c r="H347" s="14"/>
       <c r="I347" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J347" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K347" s="16"/>
@@ -8839,11 +9021,11 @@
       <c r="G348" s="14"/>
       <c r="H348" s="14"/>
       <c r="I348" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J348" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K348" s="16"/>
@@ -8861,11 +9043,11 @@
       <c r="G349" s="14"/>
       <c r="H349" s="14"/>
       <c r="I349" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J349" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K349" s="16"/>
@@ -8883,11 +9065,11 @@
       <c r="G350" s="14"/>
       <c r="H350" s="14"/>
       <c r="I350" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J350" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K350" s="16"/>
@@ -8905,11 +9087,11 @@
       <c r="G351" s="14"/>
       <c r="H351" s="14"/>
       <c r="I351" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J351" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K351" s="16"/>
@@ -8927,11 +9109,11 @@
       <c r="G352" s="14"/>
       <c r="H352" s="14"/>
       <c r="I352" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J352" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K352" s="16"/>
@@ -8949,11 +9131,11 @@
       <c r="G353" s="14"/>
       <c r="H353" s="14"/>
       <c r="I353" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J353" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K353" s="16"/>
@@ -8971,11 +9153,11 @@
       <c r="G354" s="14"/>
       <c r="H354" s="14"/>
       <c r="I354" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J354" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K354" s="16"/>
@@ -8993,11 +9175,11 @@
       <c r="G355" s="14"/>
       <c r="H355" s="14"/>
       <c r="I355" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J355" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K355" s="16"/>
@@ -9015,11 +9197,11 @@
       <c r="G356" s="14"/>
       <c r="H356" s="14"/>
       <c r="I356" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J356" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K356" s="16"/>
@@ -9037,11 +9219,11 @@
       <c r="G357" s="14"/>
       <c r="H357" s="14"/>
       <c r="I357" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J357" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K357" s="16"/>
@@ -9059,11 +9241,11 @@
       <c r="G358" s="14"/>
       <c r="H358" s="14"/>
       <c r="I358" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J358" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K358" s="16"/>
@@ -9081,11 +9263,11 @@
       <c r="G359" s="14"/>
       <c r="H359" s="14"/>
       <c r="I359" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J359" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K359" s="16"/>
@@ -9103,11 +9285,11 @@
       <c r="G360" s="14"/>
       <c r="H360" s="14"/>
       <c r="I360" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J360" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K360" s="16"/>
@@ -9125,11 +9307,11 @@
       <c r="G361" s="14"/>
       <c r="H361" s="14"/>
       <c r="I361" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J361" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K361" s="16"/>
@@ -9147,11 +9329,11 @@
       <c r="G362" s="14"/>
       <c r="H362" s="14"/>
       <c r="I362" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J362" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K362" s="16"/>
@@ -9169,11 +9351,11 @@
       <c r="G363" s="14"/>
       <c r="H363" s="14"/>
       <c r="I363" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J363" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K363" s="16"/>
@@ -9191,11 +9373,11 @@
       <c r="G364" s="14"/>
       <c r="H364" s="14"/>
       <c r="I364" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J364" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K364" s="16"/>
@@ -9213,11 +9395,11 @@
       <c r="G365" s="14"/>
       <c r="H365" s="14"/>
       <c r="I365" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J365" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K365" s="16"/>
@@ -9235,11 +9417,11 @@
       <c r="G366" s="14"/>
       <c r="H366" s="14"/>
       <c r="I366" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J366" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K366" s="16"/>
@@ -9257,11 +9439,11 @@
       <c r="G367" s="14"/>
       <c r="H367" s="14"/>
       <c r="I367" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J367" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K367" s="16"/>
@@ -9279,11 +9461,11 @@
       <c r="G368" s="14"/>
       <c r="H368" s="14"/>
       <c r="I368" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J368" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K368" s="16"/>
@@ -9301,11 +9483,11 @@
       <c r="G369" s="14"/>
       <c r="H369" s="14"/>
       <c r="I369" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J369" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K369" s="16"/>
@@ -9323,11 +9505,11 @@
       <c r="G370" s="14"/>
       <c r="H370" s="14"/>
       <c r="I370" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J370" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K370" s="16"/>
@@ -9345,11 +9527,11 @@
       <c r="G371" s="14"/>
       <c r="H371" s="14"/>
       <c r="I371" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J371" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K371" s="16"/>
@@ -9367,11 +9549,11 @@
       <c r="G372" s="14"/>
       <c r="H372" s="14"/>
       <c r="I372" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J372" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K372" s="16"/>
@@ -9389,11 +9571,11 @@
       <c r="G373" s="14"/>
       <c r="H373" s="14"/>
       <c r="I373" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J373" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K373" s="16"/>
@@ -9411,11 +9593,11 @@
       <c r="G374" s="14"/>
       <c r="H374" s="14"/>
       <c r="I374" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J374" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K374" s="16"/>
@@ -9433,11 +9615,11 @@
       <c r="G375" s="14"/>
       <c r="H375" s="14"/>
       <c r="I375" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J375" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K375" s="16"/>
@@ -9455,11 +9637,11 @@
       <c r="G376" s="14"/>
       <c r="H376" s="14"/>
       <c r="I376" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J376" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K376" s="16"/>
@@ -9477,11 +9659,11 @@
       <c r="G377" s="14"/>
       <c r="H377" s="14"/>
       <c r="I377" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J377" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K377" s="16"/>
@@ -9499,11 +9681,11 @@
       <c r="G378" s="14"/>
       <c r="H378" s="14"/>
       <c r="I378" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J378" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K378" s="16"/>
@@ -9521,11 +9703,11 @@
       <c r="G379" s="14"/>
       <c r="H379" s="14"/>
       <c r="I379" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J379" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K379" s="16"/>
@@ -9543,11 +9725,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9565,11 +9747,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9587,11 +9769,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9609,11 +9791,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9631,11 +9813,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9653,11 +9835,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I385:I396" si="14">IF(SUM(B385:F385,H385)=0,"",SUM(B385:F385,H385))</f>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J385:J396" si="15">IF(I385="","",1440-I385)</f>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9675,11 +9857,11 @@
       <c r="G386" s="14"/>
       <c r="H386" s="14"/>
       <c r="I386" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J386" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K386" s="16"/>
@@ -9697,11 +9879,11 @@
       <c r="G387" s="14"/>
       <c r="H387" s="14"/>
       <c r="I387" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J387" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K387" s="16"/>
@@ -9719,11 +9901,11 @@
       <c r="G388" s="14"/>
       <c r="H388" s="14"/>
       <c r="I388" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J388" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K388" s="16"/>
@@ -9741,11 +9923,11 @@
       <c r="G389" s="14"/>
       <c r="H389" s="14"/>
       <c r="I389" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J389" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K389" s="16"/>
@@ -9763,11 +9945,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -9785,11 +9967,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -9807,11 +9989,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -9829,11 +10011,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -9851,11 +10033,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -9873,11 +10055,11 @@
       <c r="G395" s="14"/>
       <c r="H395" s="14"/>
       <c r="I395" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J395" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K395" s="16"/>
@@ -9895,127 +10077,17 @@
       <c r="G396" s="14"/>
       <c r="H396" s="14"/>
       <c r="I396" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J396" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K396" s="16"/>
       <c r="L396" s="16"/>
       <c r="M396" s="16"/>
       <c r="N396" s="17"/>
-    </row>
-    <row r="397" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A397" s="13"/>
-      <c r="B397" s="14"/>
-      <c r="C397" s="14"/>
-      <c r="D397" s="14"/>
-      <c r="E397" s="14"/>
-      <c r="F397" s="14"/>
-      <c r="G397" s="14"/>
-      <c r="H397" s="14"/>
-      <c r="I397" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J397" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K397" s="16"/>
-      <c r="L397" s="16"/>
-      <c r="M397" s="16"/>
-      <c r="N397" s="17"/>
-    </row>
-    <row r="398" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A398" s="13"/>
-      <c r="B398" s="14"/>
-      <c r="C398" s="14"/>
-      <c r="D398" s="14"/>
-      <c r="E398" s="14"/>
-      <c r="F398" s="14"/>
-      <c r="G398" s="14"/>
-      <c r="H398" s="14"/>
-      <c r="I398" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J398" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K398" s="16"/>
-      <c r="L398" s="16"/>
-      <c r="M398" s="16"/>
-      <c r="N398" s="17"/>
-    </row>
-    <row r="399" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A399" s="13"/>
-      <c r="B399" s="14"/>
-      <c r="C399" s="14"/>
-      <c r="D399" s="14"/>
-      <c r="E399" s="14"/>
-      <c r="F399" s="14"/>
-      <c r="G399" s="14"/>
-      <c r="H399" s="14"/>
-      <c r="I399" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J399" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K399" s="16"/>
-      <c r="L399" s="16"/>
-      <c r="M399" s="16"/>
-      <c r="N399" s="17"/>
-    </row>
-    <row r="400" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A400" s="13"/>
-      <c r="B400" s="14"/>
-      <c r="C400" s="14"/>
-      <c r="D400" s="14"/>
-      <c r="E400" s="14"/>
-      <c r="F400" s="14"/>
-      <c r="G400" s="14"/>
-      <c r="H400" s="14"/>
-      <c r="I400" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J400" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K400" s="16"/>
-      <c r="L400" s="16"/>
-      <c r="M400" s="16"/>
-      <c r="N400" s="17"/>
-    </row>
-    <row r="401" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A401" s="13"/>
-      <c r="B401" s="14"/>
-      <c r="C401" s="14"/>
-      <c r="D401" s="14"/>
-      <c r="E401" s="14"/>
-      <c r="F401" s="14"/>
-      <c r="G401" s="14"/>
-      <c r="H401" s="14"/>
-      <c r="I401" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J401" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K401" s="16"/>
-      <c r="L401" s="16"/>
-      <c r="M401" s="16"/>
-      <c r="N401" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10026,21 +10098,26 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J24:J396 J6:J12">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J13:J23">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K396">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L396">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M396">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -252,10 +252,7 @@
     <t>It was great day</t>
   </si>
   <si>
-    <t>it was busy day</t>
-  </si>
-  <si>
-    <t>Today was little hectic</t>
+    <t>It was busy day</t>
   </si>
 </sst>
 </file>
@@ -442,18 +439,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -927,7 +913,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N396"/>
+  <dimension ref="A1:N391"/>
   <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1081,11 +1067,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I64" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I59" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J64" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J59" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1103,36 +1089,36 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
-        <v>46280</v>
+        <v>46285</v>
       </c>
       <c r="B7" s="14">
-        <v>400</v>
+        <v>460</v>
       </c>
       <c r="C7" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D7" s="14">
-        <v>130</v>
+        <v>300</v>
       </c>
       <c r="E7" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F7" s="14">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="G7" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H7" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>990</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>450</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>65</v>
@@ -1144,24 +1130,24 @@
         <v>57</v>
       </c>
       <c r="N7" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
-        <v>46281</v>
+        <v>46286</v>
       </c>
       <c r="B8" s="14">
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="C8" s="14">
         <v>60</v>
       </c>
       <c r="D8" s="14">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E8" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F8" s="14">
         <v>360</v>
@@ -1173,75 +1159,75 @@
         <v>60</v>
       </c>
       <c r="I8" s="15">
-        <f t="shared" si="0"/>
-        <v>1150</v>
+        <f t="shared" ref="I8:I18" si="2">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+        <v>1140</v>
       </c>
       <c r="J8" s="15">
-        <f t="shared" si="1"/>
-        <v>290</v>
+        <f t="shared" ref="J8:J18" si="3">IF(I8="","",1440-I8)</f>
+        <v>300</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L8" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M8" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N8" s="17" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
-        <v>46282</v>
+        <v>46287</v>
       </c>
       <c r="B9" s="14">
         <v>460</v>
       </c>
       <c r="C9" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="D9" s="14">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="E9" s="14">
         <v>60</v>
       </c>
       <c r="F9" s="14">
-        <v>180</v>
+        <v>420</v>
       </c>
       <c r="G9" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H9" s="14">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I9" s="15">
-        <f t="shared" si="0"/>
-        <v>1020</v>
+        <f t="shared" si="2"/>
+        <v>1170</v>
       </c>
       <c r="J9" s="15">
-        <f t="shared" si="1"/>
-        <v>420</v>
+        <f t="shared" si="3"/>
+        <v>270</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M9" s="16" t="s">
         <v>57</v>
       </c>
       <c r="N9" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
-        <v>46283</v>
+        <v>46288</v>
       </c>
       <c r="B10" s="14">
         <v>450</v>
@@ -1250,56 +1236,56 @@
         <v>60</v>
       </c>
       <c r="D10" s="14">
-        <v>250</v>
+        <v>120</v>
       </c>
       <c r="E10" s="14">
+        <v>50</v>
+      </c>
+      <c r="F10" s="14">
+        <v>360</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
         <v>60</v>
       </c>
-      <c r="F10" s="14">
-        <v>300</v>
-      </c>
-      <c r="G10" s="14">
-        <v>5</v>
-      </c>
-      <c r="H10" s="14">
-        <v>80</v>
-      </c>
       <c r="I10" s="15">
-        <f t="shared" si="0"/>
-        <v>1200</v>
+        <f t="shared" si="2"/>
+        <v>1100</v>
       </c>
       <c r="J10" s="15">
-        <f t="shared" si="1"/>
-        <v>240</v>
+        <f t="shared" si="3"/>
+        <v>340</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L10" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M10" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N10" t="s">
-        <v>70</v>
+        <v>62</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
-        <v>46284</v>
+        <v>46289</v>
       </c>
       <c r="B11" s="14">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C11" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D11" s="14">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="E11" s="14">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F11" s="14">
         <v>0</v>
@@ -1311,15 +1297,15 @@
         <v>60</v>
       </c>
       <c r="I11" s="15">
-        <f t="shared" si="0"/>
-        <v>890</v>
+        <f t="shared" si="2"/>
+        <v>750</v>
       </c>
       <c r="J11" s="15">
-        <f t="shared" si="1"/>
-        <v>550</v>
+        <f t="shared" si="3"/>
+        <v>690</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>56</v>
@@ -1328,41 +1314,41 @@
         <v>57</v>
       </c>
       <c r="N11" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
-        <v>46285</v>
+        <v>46290</v>
       </c>
       <c r="B12" s="14">
         <v>460</v>
       </c>
       <c r="C12" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="D12" s="14">
+        <v>150</v>
+      </c>
+      <c r="E12" s="14">
+        <v>60</v>
+      </c>
+      <c r="F12" s="14">
         <v>300</v>
       </c>
-      <c r="E12" s="14">
-        <v>80</v>
-      </c>
-      <c r="F12" s="14">
-        <v>0</v>
-      </c>
       <c r="G12" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H12" s="14">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="I12" s="15">
-        <f t="shared" si="0"/>
-        <v>990</v>
+        <f t="shared" si="2"/>
+        <v>1090</v>
       </c>
       <c r="J12" s="15">
-        <f t="shared" si="1"/>
-        <v>450</v>
+        <f t="shared" si="3"/>
+        <v>350</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>65</v>
@@ -1373,13 +1359,13 @@
       <c r="M12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N12" s="17" t="s">
-        <v>72</v>
+      <c r="N12" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
-        <v>46286</v>
+        <v>46291</v>
       </c>
       <c r="B13" s="14">
         <v>450</v>
@@ -1388,30 +1374,30 @@
         <v>60</v>
       </c>
       <c r="D13" s="14">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E13" s="14">
         <v>60</v>
       </c>
       <c r="F13" s="14">
-        <v>360</v>
+        <v>180</v>
       </c>
       <c r="G13" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H13" s="14">
         <v>60</v>
       </c>
       <c r="I13" s="15">
-        <f t="shared" ref="I13:I23" si="2">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v>1140</v>
+        <f t="shared" si="2"/>
+        <v>1010</v>
       </c>
       <c r="J13" s="15">
-        <f t="shared" ref="J13:J23" si="3">IF(I13="","",1440-I13)</f>
-        <v>300</v>
+        <f t="shared" si="3"/>
+        <v>430</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>56</v>
@@ -1420,58 +1406,58 @@
         <v>57</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
-        <v>46287</v>
+        <v>46292</v>
       </c>
       <c r="B14" s="14">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="C14" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D14" s="14">
-        <v>130</v>
+        <v>200</v>
       </c>
       <c r="E14" s="14">
+        <v>70</v>
+      </c>
+      <c r="F14" s="14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>0</v>
+      </c>
+      <c r="H14" s="14">
         <v>60</v>
-      </c>
-      <c r="F14" s="14">
-        <v>420</v>
-      </c>
-      <c r="G14" s="14">
-        <v>7</v>
-      </c>
-      <c r="H14" s="14">
-        <v>50</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="2"/>
-        <v>1170</v>
+        <v>840</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="3"/>
-        <v>270</v>
+        <v>600</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L14" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M14" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N14" t="s">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
-        <v>46288</v>
+        <v>46293</v>
       </c>
       <c r="B15" s="14">
         <v>450</v>
@@ -1480,27 +1466,27 @@
         <v>60</v>
       </c>
       <c r="D15" s="14">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="E15" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F15" s="14">
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="G15" s="14">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H15" s="14">
         <v>60</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="2"/>
-        <v>1100</v>
+        <v>830</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="3"/>
-        <v>340</v>
+        <v>610</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>55</v>
@@ -1509,27 +1495,27 @@
         <v>55</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="N15" s="17" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="N15" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
-        <v>46289</v>
+        <v>46294</v>
       </c>
       <c r="B16" s="14">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="C16" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D16" s="14">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F16" s="14">
         <v>0</v>
@@ -1538,15 +1524,15 @@
         <v>0</v>
       </c>
       <c r="H16" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="2"/>
-        <v>750</v>
+        <v>870</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="3"/>
-        <v>690</v>
+        <v>570</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>55</v>
@@ -1558,41 +1544,41 @@
         <v>57</v>
       </c>
       <c r="N16" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
-        <v>46290</v>
+        <v>46295</v>
       </c>
       <c r="B17" s="14">
-        <v>460</v>
+        <v>420</v>
       </c>
       <c r="C17" s="14">
         <v>60</v>
       </c>
       <c r="D17" s="14">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="E17" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="F17" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G17" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H17" s="14">
         <v>60</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="2"/>
-        <v>1090</v>
+        <v>860</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="3"/>
-        <v>350</v>
+        <v>580</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>65</v>
@@ -1604,41 +1590,41 @@
         <v>57</v>
       </c>
       <c r="N17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
-        <v>46291</v>
+        <v>46296</v>
       </c>
       <c r="B18" s="14">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="C18" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D18" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E18" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F18" s="14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="2"/>
-        <v>1010</v>
+        <v>990</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="3"/>
-        <v>430</v>
+        <v>450</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>65</v>
@@ -1650,24 +1636,24 @@
         <v>57</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
-        <v>46292</v>
+        <v>46297</v>
       </c>
       <c r="B19" s="14">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C19" s="14">
         <v>60</v>
       </c>
       <c r="D19" s="14">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="E19" s="14">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="F19" s="14">
         <v>0</v>
@@ -1676,212 +1662,116 @@
         <v>0</v>
       </c>
       <c r="H19" s="14">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="I19" s="15">
-        <f t="shared" si="2"/>
-        <v>840</v>
+        <f t="shared" si="0"/>
+        <v>910</v>
       </c>
       <c r="J19" s="15">
-        <f t="shared" si="3"/>
-        <v>600</v>
+        <f t="shared" si="1"/>
+        <v>530</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13">
-        <v>46293</v>
-      </c>
-      <c r="B20" s="14">
-        <v>450</v>
-      </c>
-      <c r="C20" s="14">
-        <v>60</v>
-      </c>
-      <c r="D20" s="14">
-        <v>200</v>
-      </c>
-      <c r="E20" s="14">
-        <v>60</v>
-      </c>
-      <c r="F20" s="14">
-        <v>0</v>
-      </c>
-      <c r="G20" s="14">
-        <v>0</v>
-      </c>
-      <c r="H20" s="14">
-        <v>60</v>
-      </c>
-      <c r="I20" s="15">
-        <f t="shared" si="2"/>
-        <v>830</v>
-      </c>
-      <c r="J20" s="15">
-        <f t="shared" si="3"/>
-        <v>610</v>
-      </c>
-      <c r="K20" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="L20" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="M20" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N20" t="s">
-        <v>69</v>
-      </c>
+      <c r="A20" s="13"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J20" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="17"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13">
-        <v>46294</v>
-      </c>
-      <c r="B21" s="14">
-        <v>420</v>
-      </c>
-      <c r="C21" s="14">
-        <v>60</v>
-      </c>
-      <c r="D21" s="14">
-        <v>250</v>
-      </c>
-      <c r="E21" s="14">
-        <v>60</v>
-      </c>
-      <c r="F21" s="14">
-        <v>0</v>
-      </c>
-      <c r="G21" s="14">
-        <v>0</v>
-      </c>
-      <c r="H21" s="14">
-        <v>80</v>
-      </c>
-      <c r="I21" s="15">
-        <f t="shared" si="2"/>
-        <v>870</v>
-      </c>
-      <c r="J21" s="15">
-        <f t="shared" si="3"/>
-        <v>570</v>
-      </c>
-      <c r="K21" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="L21" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="M21" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N21" t="s">
-        <v>70</v>
-      </c>
+      <c r="A21" s="13"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J21" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="16"/>
+      <c r="N21" s="17"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13">
-        <v>46295</v>
-      </c>
-      <c r="B22" s="14">
-        <v>420</v>
-      </c>
-      <c r="C22" s="14">
-        <v>60</v>
-      </c>
-      <c r="D22" s="14">
-        <v>250</v>
-      </c>
-      <c r="E22" s="14">
-        <v>70</v>
-      </c>
-      <c r="F22" s="14">
-        <v>0</v>
-      </c>
-      <c r="G22" s="14">
-        <v>0</v>
-      </c>
-      <c r="H22" s="14">
-        <v>60</v>
-      </c>
-      <c r="I22" s="15">
-        <f t="shared" si="2"/>
-        <v>860</v>
-      </c>
-      <c r="J22" s="15">
-        <f t="shared" si="3"/>
-        <v>580</v>
-      </c>
-      <c r="K22" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="L22" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="M22" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N22" t="s">
-        <v>71</v>
-      </c>
+      <c r="A22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J22" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="17"/>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13">
-        <v>46296</v>
-      </c>
-      <c r="B23" s="14">
-        <v>460</v>
-      </c>
-      <c r="C23" s="14">
-        <v>70</v>
-      </c>
-      <c r="D23" s="14">
-        <v>300</v>
-      </c>
-      <c r="E23" s="14">
-        <v>80</v>
-      </c>
-      <c r="F23" s="14">
-        <v>0</v>
-      </c>
-      <c r="G23" s="14">
-        <v>0</v>
-      </c>
-      <c r="H23" s="14">
-        <v>80</v>
-      </c>
-      <c r="I23" s="15">
-        <f t="shared" si="2"/>
-        <v>990</v>
-      </c>
-      <c r="J23" s="15">
-        <f t="shared" si="3"/>
-        <v>450</v>
-      </c>
-      <c r="K23" s="16" t="s">
-        <v>65</v>
-      </c>
-      <c r="L23" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="M23" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="N23" s="17" t="s">
-        <v>72</v>
-      </c>
+      <c r="A23" s="13"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="J23" s="15" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="16"/>
+      <c r="N23" s="17"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="13"/>
@@ -2685,11 +2575,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I60:I123" si="4">IF(SUM(B60:F60,H60)=0,"",SUM(B60:F60,H60))</f>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J60:J123" si="5">IF(I60="","",1440-I60)</f>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -2707,11 +2597,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -2729,11 +2619,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -2751,11 +2641,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -2773,11 +2663,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -2795,11 +2685,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" ref="I65:I128" si="4">IF(SUM(B65:F65,H65)=0,"",SUM(B65:F65,H65))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" ref="J65:J128" si="5">IF(I65="","",1440-I65)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -4093,11 +3983,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I124:I187" si="6">IF(SUM(B124:F124,H124)=0,"",SUM(B124:F124,H124))</f>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J124:J187" si="7">IF(I124="","",1440-I124)</f>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4115,11 +4005,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4137,11 +4027,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4159,11 +4049,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4181,11 +4071,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4203,11 +4093,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" ref="I129:I192" si="6">IF(SUM(B129:F129,H129)=0,"",SUM(B129:F129,H129))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" ref="J129:J192" si="7">IF(I129="","",1440-I129)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5501,11 +5391,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I188:I251" si="8">IF(SUM(B188:F188,H188)=0,"",SUM(B188:F188,H188))</f>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J188:J251" si="9">IF(I188="","",1440-I188)</f>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5523,11 +5413,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5545,11 +5435,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5567,11 +5457,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5589,11 +5479,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5611,11 +5501,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" ref="I193:I256" si="8">IF(SUM(B193:F193,H193)=0,"",SUM(B193:F193,H193))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" ref="J193:J256" si="9">IF(I193="","",1440-I193)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6909,11 +6799,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I252:I315" si="10">IF(SUM(B252:F252,H252)=0,"",SUM(B252:F252,H252))</f>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J252:J315" si="11">IF(I252="","",1440-I252)</f>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6931,11 +6821,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6953,11 +6843,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6975,11 +6865,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6997,11 +6887,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7019,11 +6909,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" ref="I257:I320" si="10">IF(SUM(B257:F257,H257)=0,"",SUM(B257:F257,H257))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" ref="J257:J320" si="11">IF(I257="","",1440-I257)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8317,11 +8207,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I316:I379" si="12">IF(SUM(B316:F316,H316)=0,"",SUM(B316:F316,H316))</f>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J316:J379" si="13">IF(I316="","",1440-I316)</f>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8339,11 +8229,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8361,11 +8251,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8383,11 +8273,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8405,11 +8295,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8427,11 +8317,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" ref="I321:I384" si="12">IF(SUM(B321:F321,H321)=0,"",SUM(B321:F321,H321))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" ref="J321:J384" si="13">IF(I321="","",1440-I321)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9725,11 +9615,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I380:I391" si="14">IF(SUM(B380:F380,H380)=0,"",SUM(B380:F380,H380))</f>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J380:J391" si="15">IF(I380="","",1440-I380)</f>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9747,11 +9637,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9769,11 +9659,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9791,11 +9681,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9813,11 +9703,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9835,11 +9725,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" ref="I385:I396" si="14">IF(SUM(B385:F385,H385)=0,"",SUM(B385:F385,H385))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" ref="J385:J396" si="15">IF(I385="","",1440-I385)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9979,116 +9869,6 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A392" s="13"/>
-      <c r="B392" s="14"/>
-      <c r="C392" s="14"/>
-      <c r="D392" s="14"/>
-      <c r="E392" s="14"/>
-      <c r="F392" s="14"/>
-      <c r="G392" s="14"/>
-      <c r="H392" s="14"/>
-      <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K392" s="16"/>
-      <c r="L392" s="16"/>
-      <c r="M392" s="16"/>
-      <c r="N392" s="17"/>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A393" s="13"/>
-      <c r="B393" s="14"/>
-      <c r="C393" s="14"/>
-      <c r="D393" s="14"/>
-      <c r="E393" s="14"/>
-      <c r="F393" s="14"/>
-      <c r="G393" s="14"/>
-      <c r="H393" s="14"/>
-      <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K393" s="16"/>
-      <c r="L393" s="16"/>
-      <c r="M393" s="16"/>
-      <c r="N393" s="17"/>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A394" s="13"/>
-      <c r="B394" s="14"/>
-      <c r="C394" s="14"/>
-      <c r="D394" s="14"/>
-      <c r="E394" s="14"/>
-      <c r="F394" s="14"/>
-      <c r="G394" s="14"/>
-      <c r="H394" s="14"/>
-      <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K394" s="16"/>
-      <c r="L394" s="16"/>
-      <c r="M394" s="16"/>
-      <c r="N394" s="17"/>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A395" s="13"/>
-      <c r="B395" s="14"/>
-      <c r="C395" s="14"/>
-      <c r="D395" s="14"/>
-      <c r="E395" s="14"/>
-      <c r="F395" s="14"/>
-      <c r="G395" s="14"/>
-      <c r="H395" s="14"/>
-      <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K395" s="16"/>
-      <c r="L395" s="16"/>
-      <c r="M395" s="16"/>
-      <c r="N395" s="17"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A396" s="13"/>
-      <c r="B396" s="14"/>
-      <c r="C396" s="14"/>
-      <c r="D396" s="14"/>
-      <c r="E396" s="14"/>
-      <c r="F396" s="14"/>
-      <c r="G396" s="14"/>
-      <c r="H396" s="14"/>
-      <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K396" s="16"/>
-      <c r="L396" s="16"/>
-      <c r="M396" s="16"/>
-      <c r="N396" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10098,26 +9878,26 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J24:J396 J6:J12">
+  <conditionalFormatting sqref="J19:J391 J6:J7">
     <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J13:J23">
+  <conditionalFormatting sqref="J8:J18">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K396">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K391">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L396">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L391">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M396">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M391">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="-105" windowWidth="19425" windowHeight="10425" tabRatio="500" activeTab="1"/>
@@ -11,27 +11,11 @@
     <sheet name="Daily Log" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="144525" iterateDelta="1E-4"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +238,12 @@
   <si>
     <t>It was busy day</t>
   </si>
+  <si>
+    <t>it was busy day</t>
+  </si>
+  <si>
+    <t>Today was little hectic</t>
+  </si>
 </sst>
 </file>
 
@@ -391,7 +381,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -435,11 +425,104 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -535,9 +618,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -913,8 +993,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N391"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N396"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="6" width="11" customWidth="1"/>
@@ -1067,11 +1147,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I59" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I64" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J59" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J64" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1087,735 +1167,869 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="13">
+    <row r="7" spans="1:14" s="22" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="23">
+        <v>46280</v>
+      </c>
+      <c r="B7" s="24">
+        <v>400</v>
+      </c>
+      <c r="C7" s="24">
+        <v>60</v>
+      </c>
+      <c r="D7" s="24">
+        <v>130</v>
+      </c>
+      <c r="E7" s="24">
+        <v>60</v>
+      </c>
+      <c r="F7" s="24">
+        <v>420</v>
+      </c>
+      <c r="G7" s="24">
+        <v>7</v>
+      </c>
+      <c r="H7" s="24">
+        <v>60</v>
+      </c>
+      <c r="I7" s="25">
+        <v>1130</v>
+      </c>
+      <c r="J7" s="25">
+        <v>310</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="L7" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="N7" s="27" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="28">
+        <v>46281</v>
+      </c>
+      <c r="B8" s="29">
+        <v>430</v>
+      </c>
+      <c r="C8" s="29">
+        <v>60</v>
+      </c>
+      <c r="D8" s="29">
+        <v>170</v>
+      </c>
+      <c r="E8" s="29">
+        <v>70</v>
+      </c>
+      <c r="F8" s="29">
+        <v>360</v>
+      </c>
+      <c r="G8" s="29">
+        <v>6</v>
+      </c>
+      <c r="H8" s="29">
+        <v>60</v>
+      </c>
+      <c r="I8" s="30">
+        <v>1150</v>
+      </c>
+      <c r="J8" s="30">
+        <v>290</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="34">
+        <v>46282</v>
+      </c>
+      <c r="B9" s="35">
+        <v>460</v>
+      </c>
+      <c r="C9" s="35">
+        <v>60</v>
+      </c>
+      <c r="D9" s="35">
+        <v>200</v>
+      </c>
+      <c r="E9" s="35">
+        <v>60</v>
+      </c>
+      <c r="F9" s="35">
+        <v>180</v>
+      </c>
+      <c r="G9" s="35">
+        <v>3</v>
+      </c>
+      <c r="H9" s="35">
+        <v>60</v>
+      </c>
+      <c r="I9" s="36">
+        <v>1020</v>
+      </c>
+      <c r="J9" s="36">
+        <v>420</v>
+      </c>
+      <c r="K9" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="33" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="39">
+        <v>46283</v>
+      </c>
+      <c r="B10" s="40">
+        <v>450</v>
+      </c>
+      <c r="C10" s="40">
+        <v>60</v>
+      </c>
+      <c r="D10" s="40">
+        <v>250</v>
+      </c>
+      <c r="E10" s="40">
+        <v>60</v>
+      </c>
+      <c r="F10" s="40">
+        <v>300</v>
+      </c>
+      <c r="G10" s="40">
+        <v>5</v>
+      </c>
+      <c r="H10" s="40">
+        <v>80</v>
+      </c>
+      <c r="I10" s="41">
+        <v>1200</v>
+      </c>
+      <c r="J10" s="41">
+        <v>240</v>
+      </c>
+      <c r="K10" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="42" t="s">
+        <v>56</v>
+      </c>
+      <c r="M10" s="42" t="s">
+        <v>57</v>
+      </c>
+      <c r="N10" s="38" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="44">
+        <v>46284</v>
+      </c>
+      <c r="B11" s="45">
+        <v>450</v>
+      </c>
+      <c r="C11" s="45">
+        <v>60</v>
+      </c>
+      <c r="D11" s="45">
+        <v>250</v>
+      </c>
+      <c r="E11" s="45">
+        <v>70</v>
+      </c>
+      <c r="F11" s="45">
+        <v>0</v>
+      </c>
+      <c r="G11" s="45">
+        <v>0</v>
+      </c>
+      <c r="H11" s="45">
+        <v>60</v>
+      </c>
+      <c r="I11" s="46">
+        <v>890</v>
+      </c>
+      <c r="J11" s="46">
+        <v>550</v>
+      </c>
+      <c r="K11" s="47" t="s">
+        <v>65</v>
+      </c>
+      <c r="L11" s="47" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="N11" s="43" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A12" s="13">
         <v>46285</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B12" s="14">
         <v>460</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C12" s="14">
         <v>70</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D12" s="14">
         <v>300</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E12" s="14">
         <v>80</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F12" s="14">
         <v>0</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G12" s="14">
         <v>0</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H12" s="14">
         <v>80</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
         <v>990</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>450</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K12" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L12" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N12" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="13">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" s="13">
         <v>46286</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B13" s="14">
         <v>450</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C13" s="14">
         <v>60</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D13" s="14">
         <v>150</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E13" s="14">
         <v>60</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F13" s="14">
         <v>360</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G13" s="14">
         <v>6</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H13" s="14">
         <v>60</v>
       </c>
-      <c r="I8" s="15">
-        <f t="shared" ref="I8:I18" si="2">IF(SUM(B8:F8,H8)=0,"",SUM(B8:F8,H8))</f>
+      <c r="I13" s="15">
+        <f t="shared" ref="I13:I23" si="2">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
         <v>1140</v>
       </c>
-      <c r="J8" s="15">
-        <f t="shared" ref="J8:J18" si="3">IF(I8="","",1440-I8)</f>
+      <c r="J13" s="15">
+        <f t="shared" ref="J13:J23" si="3">IF(I13="","",1440-I13)</f>
         <v>300</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N13" s="17" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="13">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="13">
         <v>46287</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B14" s="14">
         <v>460</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C14" s="14">
         <v>50</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D14" s="14">
         <v>130</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E14" s="14">
         <v>60</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F14" s="14">
         <v>420</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G14" s="14">
         <v>7</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H14" s="14">
         <v>50</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I14" s="15">
         <f t="shared" si="2"/>
         <v>1170</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J14" s="15">
         <f t="shared" si="3"/>
         <v>270</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K14" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N14" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="13">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="13">
         <v>46288</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B15" s="14">
         <v>450</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C15" s="14">
         <v>60</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D15" s="14">
         <v>120</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E15" s="14">
         <v>50</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F15" s="14">
         <v>360</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G15" s="14">
         <v>6</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H15" s="14">
         <v>60</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I15" s="15">
         <f t="shared" si="2"/>
         <v>1100</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J15" s="15">
         <f t="shared" si="3"/>
         <v>340</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L15" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N15" s="17" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="13">
         <v>46289</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B16" s="14">
         <v>460</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C16" s="14">
         <v>30</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D16" s="14">
         <v>150</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E16" s="14">
         <v>50</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F16" s="14">
         <v>0</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G16" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H16" s="14">
         <v>60</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I16" s="15">
         <f t="shared" si="2"/>
         <v>750</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J16" s="15">
         <f t="shared" si="3"/>
         <v>690</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K16" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L16" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M16" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N11" t="s">
+      <c r="N16" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="13">
         <v>46290</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B17" s="14">
         <v>460</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C17" s="14">
         <v>60</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D17" s="14">
         <v>150</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E17" s="14">
         <v>60</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F17" s="14">
         <v>300</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G17" s="14">
         <v>5</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H17" s="14">
         <v>60</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I17" s="15">
         <f t="shared" si="2"/>
         <v>1090</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J17" s="15">
         <f t="shared" si="3"/>
         <v>350</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K17" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L17" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M17" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N12" t="s">
+      <c r="N17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A18" s="13">
         <v>46291</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B18" s="14">
         <v>450</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C18" s="14">
         <v>60</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D18" s="14">
         <v>200</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E18" s="14">
         <v>60</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F18" s="14">
         <v>180</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G18" s="14">
         <v>3</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H18" s="14">
         <v>60</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I18" s="15">
         <f t="shared" si="2"/>
         <v>1010</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J18" s="15">
         <f t="shared" si="3"/>
         <v>430</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K18" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L18" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M18" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N18" s="17" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A19" s="13">
         <v>46292</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B19" s="14">
         <v>450</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C19" s="14">
         <v>60</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D19" s="14">
         <v>200</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E19" s="14">
         <v>70</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F19" s="14">
         <v>0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G19" s="14">
         <v>0</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H19" s="14">
         <v>60</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I19" s="15">
         <f t="shared" si="2"/>
         <v>840</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J19" s="15">
         <f t="shared" si="3"/>
         <v>600</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K19" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L19" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M19" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N19" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
         <v>46293</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B20" s="14">
         <v>450</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C20" s="14">
         <v>60</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D20" s="14">
         <v>200</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E20" s="14">
         <v>60</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F20" s="14">
         <v>0</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G20" s="14">
         <v>0</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H20" s="14">
         <v>60</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I20" s="15">
         <f t="shared" si="2"/>
         <v>830</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J20" s="15">
         <f t="shared" si="3"/>
         <v>610</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K20" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="L20" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M20" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N15" t="s">
+      <c r="N20" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A21" s="13">
         <v>46294</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B21" s="14">
         <v>420</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C21" s="14">
         <v>60</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D21" s="14">
         <v>250</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E21" s="14">
         <v>60</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F21" s="14">
         <v>0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G21" s="14">
         <v>0</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H21" s="14">
         <v>80</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I21" s="15">
         <f t="shared" si="2"/>
         <v>870</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J21" s="15">
         <f t="shared" si="3"/>
         <v>570</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K21" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="L21" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M21" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N21" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A22" s="13">
         <v>46295</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B22" s="14">
         <v>420</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C22" s="14">
         <v>60</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D22" s="14">
         <v>250</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E22" s="14">
         <v>70</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F22" s="14">
         <v>0</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G22" s="14">
         <v>0</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H22" s="14">
         <v>60</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I22" s="15">
         <f t="shared" si="2"/>
         <v>860</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J22" s="15">
         <f t="shared" si="3"/>
         <v>580</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K22" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="L22" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M22" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N17" t="s">
+      <c r="N22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="13">
         <v>46296</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B23" s="14">
         <v>460</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C23" s="14">
         <v>70</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D23" s="14">
         <v>300</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E23" s="14">
         <v>80</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F23" s="14">
         <v>0</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G23" s="14">
         <v>0</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H23" s="14">
         <v>80</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I23" s="15">
         <f t="shared" si="2"/>
         <v>990</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J23" s="15">
         <f t="shared" si="3"/>
         <v>450</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K23" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="L23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M23" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N23" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" s="13">
         <v>46297</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B24" s="14">
         <v>430</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C24" s="14">
         <v>60</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D24" s="14">
         <v>300</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E24" s="14">
         <v>50</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F24" s="14">
         <v>0</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G24" s="14">
         <v>0</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H24" s="14">
         <v>70</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
         <v>910</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
         <v>530</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K24" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="L24" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="M24" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N19" s="17" t="s">
+      <c r="N24" s="17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A25" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B25" s="14">
+        <v>450</v>
+      </c>
+      <c r="C25" s="14">
+        <v>60</v>
+      </c>
+      <c r="D25" s="14">
+        <v>300</v>
+      </c>
+      <c r="E25" s="14">
+        <v>60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>0</v>
+      </c>
+      <c r="H25" s="14">
+        <v>40</v>
+      </c>
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="13"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J22" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="17"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="13"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J23" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" s="16"/>
-      <c r="N23" s="17"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="13"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J24" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" s="16"/>
-      <c r="N24" s="17"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="13"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J25" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" s="16"/>
-      <c r="N25" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="L25" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M25" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="13"/>
@@ -2575,11 +2789,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" ref="I60:I123" si="4">IF(SUM(B60:F60,H60)=0,"",SUM(B60:F60,H60))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
-        <f t="shared" ref="J60:J123" si="5">IF(I60="","",1440-I60)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -2597,11 +2811,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -2619,11 +2833,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -2641,11 +2855,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -2663,11 +2877,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -2685,11 +2899,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I65:I128" si="4">IF(SUM(B65:F65,H65)=0,"",SUM(B65:F65,H65))</f>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J65:J128" si="5">IF(I65="","",1440-I65)</f>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -3983,11 +4197,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" ref="I124:I187" si="6">IF(SUM(B124:F124,H124)=0,"",SUM(B124:F124,H124))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" ref="J124:J187" si="7">IF(I124="","",1440-I124)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4005,11 +4219,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4027,11 +4241,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4049,11 +4263,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4071,11 +4285,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4093,11 +4307,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I129:I192" si="6">IF(SUM(B129:F129,H129)=0,"",SUM(B129:F129,H129))</f>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J129:J192" si="7">IF(I129="","",1440-I129)</f>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -5391,11 +5605,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" ref="I188:I251" si="8">IF(SUM(B188:F188,H188)=0,"",SUM(B188:F188,H188))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" ref="J188:J251" si="9">IF(I188="","",1440-I188)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5413,11 +5627,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5435,11 +5649,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5457,11 +5671,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5479,11 +5693,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5501,11 +5715,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I193:I256" si="8">IF(SUM(B193:F193,H193)=0,"",SUM(B193:F193,H193))</f>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J193:J256" si="9">IF(I193="","",1440-I193)</f>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -6799,11 +7013,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" ref="I252:I315" si="10">IF(SUM(B252:F252,H252)=0,"",SUM(B252:F252,H252))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" ref="J252:J315" si="11">IF(I252="","",1440-I252)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -6821,11 +7035,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -6843,11 +7057,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -6865,11 +7079,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -6887,11 +7101,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -6909,11 +7123,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I257:I320" si="10">IF(SUM(B257:F257,H257)=0,"",SUM(B257:F257,H257))</f>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J257:J320" si="11">IF(I257="","",1440-I257)</f>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -8207,11 +8421,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" ref="I316:I379" si="12">IF(SUM(B316:F316,H316)=0,"",SUM(B316:F316,H316))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" ref="J316:J379" si="13">IF(I316="","",1440-I316)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8229,11 +8443,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8251,11 +8465,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8273,11 +8487,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8295,11 +8509,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8317,11 +8531,11 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I321:I384" si="12">IF(SUM(B321:F321,H321)=0,"",SUM(B321:F321,H321))</f>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J321:J384" si="13">IF(I321="","",1440-I321)</f>
         <v/>
       </c>
       <c r="K321" s="16"/>
@@ -9615,11 +9829,11 @@
       <c r="G380" s="14"/>
       <c r="H380" s="14"/>
       <c r="I380" s="15" t="str">
-        <f t="shared" ref="I380:I391" si="14">IF(SUM(B380:F380,H380)=0,"",SUM(B380:F380,H380))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J380" s="15" t="str">
-        <f t="shared" ref="J380:J391" si="15">IF(I380="","",1440-I380)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K380" s="16"/>
@@ -9637,11 +9851,11 @@
       <c r="G381" s="14"/>
       <c r="H381" s="14"/>
       <c r="I381" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J381" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K381" s="16"/>
@@ -9659,11 +9873,11 @@
       <c r="G382" s="14"/>
       <c r="H382" s="14"/>
       <c r="I382" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J382" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K382" s="16"/>
@@ -9681,11 +9895,11 @@
       <c r="G383" s="14"/>
       <c r="H383" s="14"/>
       <c r="I383" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J383" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K383" s="16"/>
@@ -9703,11 +9917,11 @@
       <c r="G384" s="14"/>
       <c r="H384" s="14"/>
       <c r="I384" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J384" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K384" s="16"/>
@@ -9725,11 +9939,11 @@
       <c r="G385" s="14"/>
       <c r="H385" s="14"/>
       <c r="I385" s="15" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="I385:I396" si="14">IF(SUM(B385:F385,H385)=0,"",SUM(B385:F385,H385))</f>
         <v/>
       </c>
       <c r="J385" s="15" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="J385:J396" si="15">IF(I385="","",1440-I385)</f>
         <v/>
       </c>
       <c r="K385" s="16"/>
@@ -9869,6 +10083,116 @@
       <c r="M391" s="16"/>
       <c r="N391" s="17"/>
     </row>
+    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A392" s="13"/>
+      <c r="B392" s="14"/>
+      <c r="C392" s="14"/>
+      <c r="D392" s="14"/>
+      <c r="E392" s="14"/>
+      <c r="F392" s="14"/>
+      <c r="G392" s="14"/>
+      <c r="H392" s="14"/>
+      <c r="I392" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J392" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K392" s="16"/>
+      <c r="L392" s="16"/>
+      <c r="M392" s="16"/>
+      <c r="N392" s="17"/>
+    </row>
+    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A393" s="13"/>
+      <c r="B393" s="14"/>
+      <c r="C393" s="14"/>
+      <c r="D393" s="14"/>
+      <c r="E393" s="14"/>
+      <c r="F393" s="14"/>
+      <c r="G393" s="14"/>
+      <c r="H393" s="14"/>
+      <c r="I393" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J393" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K393" s="16"/>
+      <c r="L393" s="16"/>
+      <c r="M393" s="16"/>
+      <c r="N393" s="17"/>
+    </row>
+    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A394" s="13"/>
+      <c r="B394" s="14"/>
+      <c r="C394" s="14"/>
+      <c r="D394" s="14"/>
+      <c r="E394" s="14"/>
+      <c r="F394" s="14"/>
+      <c r="G394" s="14"/>
+      <c r="H394" s="14"/>
+      <c r="I394" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J394" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K394" s="16"/>
+      <c r="L394" s="16"/>
+      <c r="M394" s="16"/>
+      <c r="N394" s="17"/>
+    </row>
+    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A395" s="13"/>
+      <c r="B395" s="14"/>
+      <c r="C395" s="14"/>
+      <c r="D395" s="14"/>
+      <c r="E395" s="14"/>
+      <c r="F395" s="14"/>
+      <c r="G395" s="14"/>
+      <c r="H395" s="14"/>
+      <c r="I395" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J395" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K395" s="16"/>
+      <c r="L395" s="16"/>
+      <c r="M395" s="16"/>
+      <c r="N395" s="17"/>
+    </row>
+    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A396" s="13"/>
+      <c r="B396" s="14"/>
+      <c r="C396" s="14"/>
+      <c r="D396" s="14"/>
+      <c r="E396" s="14"/>
+      <c r="F396" s="14"/>
+      <c r="G396" s="14"/>
+      <c r="H396" s="14"/>
+      <c r="I396" s="15" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="J396" s="15" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+      <c r="K396" s="16"/>
+      <c r="L396" s="16"/>
+      <c r="M396" s="16"/>
+      <c r="N396" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -9878,26 +10202,31 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J19:J391 J6:J7">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J24:J396 J6 J8:J12">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J8:J18">
+  <conditionalFormatting sqref="J13:J23">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K391">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K396">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L391">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L396">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M391">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M396">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/1234567.xlsx
+++ b/1234567.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="78">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -244,6 +244,12 @@
   <si>
     <t>Today was little hectic</t>
   </si>
+  <si>
+    <t>great</t>
+  </si>
+  <si>
+    <t>It was a pretty normal day</t>
+  </si>
 </sst>
 </file>
 
@@ -422,9 +428,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -496,22 +499,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -993,7 +988,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N396"/>
+  <dimension ref="A1:N321"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1008,74 +1003,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
     </row>
     <row r="2" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="47" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
       <c r="E2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="47">
         <v>12629031</v>
       </c>
-      <c r="G2" s="20"/>
+      <c r="G2" s="47"/>
     </row>
     <row r="3" spans="1:14" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="47" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
       <c r="E3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="G3" s="20"/>
+      <c r="G3" s="47"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="J4" s="18"/>
-      <c r="K4" s="18"/>
-      <c r="L4" s="18"/>
-      <c r="M4" s="18"/>
-      <c r="N4" s="18"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
     </row>
     <row r="5" spans="1:14" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
@@ -1147,11 +1142,11 @@
         <v>30</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I64" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <f t="shared" ref="I6:I25" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
         <v>885</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J64" si="1">IF(I6="","",1440-I6)</f>
+        <f t="shared" ref="J6:J25" si="1">IF(I6="","",1440-I6)</f>
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1167,223 +1162,223 @@
         <v>52</v>
       </c>
     </row>
-    <row r="7" spans="1:14" s="22" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23">
+    <row r="7" spans="1:14" s="19" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
         <v>46280</v>
       </c>
-      <c r="B7" s="24">
+      <c r="B7" s="21">
         <v>400</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="21">
         <v>60</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="21">
         <v>130</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="21">
         <v>60</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="21">
         <v>420</v>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="21">
         <v>7</v>
       </c>
-      <c r="H7" s="24">
+      <c r="H7" s="21">
         <v>60</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="22">
         <v>1130</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="22">
         <v>310</v>
       </c>
-      <c r="K7" s="26" t="s">
+      <c r="K7" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="L7" s="26" t="s">
+      <c r="L7" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="M7" s="26" t="s">
+      <c r="M7" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="N7" s="27" t="s">
+      <c r="N7" s="24" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="28">
+    <row r="8" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25">
         <v>46281</v>
       </c>
-      <c r="B8" s="29">
+      <c r="B8" s="26">
         <v>430</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="26">
         <v>60</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="26">
         <v>170</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="26">
         <v>70</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="26">
         <v>360</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="26">
         <v>6</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="26">
         <v>60</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="27">
         <v>1150</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="27">
         <v>290</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="K8" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="L8" s="31" t="s">
+      <c r="L8" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="M8" s="31" t="s">
+      <c r="M8" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="N8" s="32" t="s">
+      <c r="N8" s="29" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="9" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="34">
+    <row r="9" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="31">
         <v>46282</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="32">
         <v>460</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="32">
         <v>60</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="32">
         <v>200</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="32">
         <v>60</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="32">
         <v>180</v>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="32">
         <v>3</v>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="32">
         <v>60</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="33">
         <v>1020</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="33">
         <v>420</v>
       </c>
-      <c r="K9" s="37" t="s">
+      <c r="K9" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="M9" s="37" t="s">
+      <c r="M9" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="N9" s="30" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="39">
+    <row r="10" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36">
         <v>46283</v>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="37">
         <v>450</v>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="37">
         <v>60</v>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="37">
         <v>250</v>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="37">
         <v>60</v>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="37">
         <v>300</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="37">
         <v>5</v>
       </c>
-      <c r="H10" s="40">
+      <c r="H10" s="37">
         <v>80</v>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="38">
         <v>1200</v>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="38">
         <v>240</v>
       </c>
-      <c r="K10" s="42" t="s">
+      <c r="K10" s="39" t="s">
         <v>55</v>
       </c>
-      <c r="L10" s="42" t="s">
+      <c r="L10" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="M10" s="42" t="s">
+      <c r="M10" s="39" t="s">
         <v>57</v>
       </c>
-      <c r="N10" s="38" t="s">
+      <c r="N10" s="35" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:14" s="21" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="44">
+    <row r="11" spans="1:14" s="18" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="41">
         <v>46284</v>
       </c>
-      <c r="B11" s="45">
+      <c r="B11" s="42">
         <v>450</v>
       </c>
-      <c r="C11" s="45">
+      <c r="C11" s="42">
         <v>60</v>
       </c>
-      <c r="D11" s="45">
+      <c r="D11" s="42">
         <v>250</v>
       </c>
-      <c r="E11" s="45">
+      <c r="E11" s="42">
         <v>70</v>
       </c>
-      <c r="F11" s="45">
+      <c r="F11" s="42">
         <v>0</v>
       </c>
-      <c r="G11" s="45">
+      <c r="G11" s="42">
         <v>0</v>
       </c>
-      <c r="H11" s="45">
+      <c r="H11" s="42">
         <v>60</v>
       </c>
-      <c r="I11" s="46">
+      <c r="I11" s="43">
         <v>890</v>
       </c>
-      <c r="J11" s="46">
+      <c r="J11" s="43">
         <v>550</v>
       </c>
-      <c r="K11" s="47" t="s">
+      <c r="K11" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="L11" s="47" t="s">
+      <c r="L11" s="44" t="s">
         <v>56</v>
       </c>
-      <c r="M11" s="47" t="s">
+      <c r="M11" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="N11" s="43" t="s">
+      <c r="N11" s="40" t="s">
         <v>71</v>
       </c>
     </row>
@@ -2032,26 +2027,50 @@
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A26" s="13"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J26" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" s="16"/>
-      <c r="N26" s="17"/>
+      <c r="A26" s="13">
+        <v>46299</v>
+      </c>
+      <c r="B26" s="14">
+        <v>420</v>
+      </c>
+      <c r="C26" s="14">
+        <v>40</v>
+      </c>
+      <c r="D26" s="14">
+        <v>130</v>
+      </c>
+      <c r="E26" s="14">
+        <v>60</v>
+      </c>
+      <c r="F26" s="14">
+        <v>0</v>
+      </c>
+      <c r="G26" s="14">
+        <v>0</v>
+      </c>
+      <c r="H26" s="14">
+        <v>60</v>
+      </c>
+      <c r="I26" s="15">
+        <f t="shared" ref="I26:I53" si="4">IF(SUM(B26:F26,H26)=0,"",SUM(B26:F26,H26))</f>
+        <v>710</v>
+      </c>
+      <c r="J26" s="15">
+        <f t="shared" ref="J26:J53" si="5">IF(I26="","",1440-I26)</f>
+        <v>730</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M26" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N26" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="13"/>
@@ -2063,11 +2082,11 @@
       <c r="G27" s="14"/>
       <c r="H27" s="14"/>
       <c r="I27" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J27" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K27" s="16"/>
@@ -2085,11 +2104,11 @@
       <c r="G28" s="14"/>
       <c r="H28" s="14"/>
       <c r="I28" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J28" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K28" s="16"/>
@@ -2107,11 +2126,11 @@
       <c r="G29" s="14"/>
       <c r="H29" s="14"/>
       <c r="I29" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J29" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K29" s="16"/>
@@ -2129,11 +2148,11 @@
       <c r="G30" s="14"/>
       <c r="H30" s="14"/>
       <c r="I30" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J30" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K30" s="16"/>
@@ -2151,11 +2170,11 @@
       <c r="G31" s="14"/>
       <c r="H31" s="14"/>
       <c r="I31" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J31" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K31" s="16"/>
@@ -2173,11 +2192,11 @@
       <c r="G32" s="14"/>
       <c r="H32" s="14"/>
       <c r="I32" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J32" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K32" s="16"/>
@@ -2195,11 +2214,11 @@
       <c r="G33" s="14"/>
       <c r="H33" s="14"/>
       <c r="I33" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J33" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K33" s="16"/>
@@ -2217,11 +2236,11 @@
       <c r="G34" s="14"/>
       <c r="H34" s="14"/>
       <c r="I34" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J34" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K34" s="16"/>
@@ -2239,11 +2258,11 @@
       <c r="G35" s="14"/>
       <c r="H35" s="14"/>
       <c r="I35" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J35" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K35" s="16"/>
@@ -2261,11 +2280,11 @@
       <c r="G36" s="14"/>
       <c r="H36" s="14"/>
       <c r="I36" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J36" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K36" s="16"/>
@@ -2283,11 +2302,11 @@
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J37" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K37" s="16"/>
@@ -2305,11 +2324,11 @@
       <c r="G38" s="14"/>
       <c r="H38" s="14"/>
       <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K38" s="16"/>
@@ -2327,11 +2346,11 @@
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K39" s="16"/>
@@ -2349,11 +2368,11 @@
       <c r="G40" s="14"/>
       <c r="H40" s="14"/>
       <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K40" s="16"/>
@@ -2371,11 +2390,11 @@
       <c r="G41" s="14"/>
       <c r="H41" s="14"/>
       <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K41" s="16"/>
@@ -2393,11 +2412,11 @@
       <c r="G42" s="14"/>
       <c r="H42" s="14"/>
       <c r="I42" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J42" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K42" s="16"/>
@@ -2415,11 +2434,11 @@
       <c r="G43" s="14"/>
       <c r="H43" s="14"/>
       <c r="I43" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J43" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K43" s="16"/>
@@ -2437,11 +2456,11 @@
       <c r="G44" s="14"/>
       <c r="H44" s="14"/>
       <c r="I44" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J44" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K44" s="16"/>
@@ -2459,11 +2478,11 @@
       <c r="G45" s="14"/>
       <c r="H45" s="14"/>
       <c r="I45" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J45" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K45" s="16"/>
@@ -2481,11 +2500,11 @@
       <c r="G46" s="14"/>
       <c r="H46" s="14"/>
       <c r="I46" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J46" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K46" s="16"/>
@@ -2503,11 +2522,11 @@
       <c r="G47" s="14"/>
       <c r="H47" s="14"/>
       <c r="I47" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J47" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K47" s="16"/>
@@ -2525,11 +2544,11 @@
       <c r="G48" s="14"/>
       <c r="H48" s="14"/>
       <c r="I48" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J48" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K48" s="16"/>
@@ -2547,11 +2566,11 @@
       <c r="G49" s="14"/>
       <c r="H49" s="14"/>
       <c r="I49" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J49" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K49" s="16"/>
@@ -2569,11 +2588,11 @@
       <c r="G50" s="14"/>
       <c r="H50" s="14"/>
       <c r="I50" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K50" s="16"/>
@@ -2591,11 +2610,11 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
       <c r="I51" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K51" s="16"/>
@@ -2613,11 +2632,11 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
       <c r="I52" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J52" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K52" s="16"/>
@@ -2635,11 +2654,11 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
       <c r="I53" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J53" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K53" s="16"/>
@@ -2657,11 +2676,11 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
       <c r="I54" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I54:I117" si="6">IF(SUM(B54:F54,H54)=0,"",SUM(B54:F54,H54))</f>
         <v/>
       </c>
       <c r="J54" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J54:J117" si="7">IF(I54="","",1440-I54)</f>
         <v/>
       </c>
       <c r="K54" s="16"/>
@@ -2679,11 +2698,11 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
       <c r="I55" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J55" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K55" s="16"/>
@@ -2701,11 +2720,11 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
       <c r="I56" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J56" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K56" s="16"/>
@@ -2723,11 +2742,11 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
       <c r="I57" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J57" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K57" s="16"/>
@@ -2745,11 +2764,11 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
       <c r="I58" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J58" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K58" s="16"/>
@@ -2767,11 +2786,11 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
       <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K59" s="16"/>
@@ -2789,11 +2808,11 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
       <c r="I60" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J60" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K60" s="16"/>
@@ -2811,11 +2830,11 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
       <c r="I61" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J61" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K61" s="16"/>
@@ -2833,11 +2852,11 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
       <c r="I62" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J62" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K62" s="16"/>
@@ -2855,11 +2874,11 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
       <c r="I63" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J63" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K63" s="16"/>
@@ -2877,11 +2896,11 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
       <c r="I64" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J64" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K64" s="16"/>
@@ -2899,11 +2918,11 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
       <c r="I65" s="15" t="str">
-        <f t="shared" ref="I65:I128" si="4">IF(SUM(B65:F65,H65)=0,"",SUM(B65:F65,H65))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J65" s="15" t="str">
-        <f t="shared" ref="J65:J128" si="5">IF(I65="","",1440-I65)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K65" s="16"/>
@@ -2921,11 +2940,11 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
       <c r="I66" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J66" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K66" s="16"/>
@@ -2943,11 +2962,11 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
       <c r="I67" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J67" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K67" s="16"/>
@@ -2965,11 +2984,11 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
       <c r="I68" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J68" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K68" s="16"/>
@@ -2987,11 +3006,11 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
       <c r="I69" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J69" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K69" s="16"/>
@@ -3009,11 +3028,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3031,11 +3050,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3053,11 +3072,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3075,11 +3094,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3097,11 +3116,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -3119,11 +3138,11 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
       <c r="I75" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J75" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K75" s="16"/>
@@ -3141,11 +3160,11 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
       <c r="I76" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J76" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K76" s="16"/>
@@ -3163,11 +3182,11 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
       <c r="I77" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J77" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K77" s="16"/>
@@ -3185,11 +3204,11 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
       <c r="I78" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J78" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K78" s="16"/>
@@ -3207,11 +3226,11 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
       <c r="I79" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J79" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K79" s="16"/>
@@ -3229,11 +3248,11 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
       <c r="I80" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J80" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K80" s="16"/>
@@ -3251,11 +3270,11 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
       <c r="I81" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J81" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K81" s="16"/>
@@ -3273,11 +3292,11 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
       <c r="I82" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J82" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K82" s="16"/>
@@ -3295,11 +3314,11 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
       <c r="I83" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J83" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K83" s="16"/>
@@ -3317,11 +3336,11 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
       <c r="I84" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J84" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K84" s="16"/>
@@ -3339,11 +3358,11 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
       <c r="I85" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J85" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K85" s="16"/>
@@ -3361,11 +3380,11 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
       <c r="I86" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J86" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K86" s="16"/>
@@ -3383,11 +3402,11 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
       <c r="I87" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J87" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K87" s="16"/>
@@ -3405,11 +3424,11 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
       <c r="I88" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J88" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K88" s="16"/>
@@ -3427,11 +3446,11 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
       <c r="I89" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J89" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K89" s="16"/>
@@ -3449,11 +3468,11 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
       <c r="I90" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J90" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K90" s="16"/>
@@ -3471,11 +3490,11 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
       <c r="I91" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J91" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K91" s="16"/>
@@ -3493,11 +3512,11 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
       <c r="I92" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J92" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K92" s="16"/>
@@ -3515,11 +3534,11 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
       <c r="I93" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J93" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K93" s="16"/>
@@ -3537,11 +3556,11 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
       <c r="I94" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J94" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K94" s="16"/>
@@ -3559,11 +3578,11 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
       <c r="I95" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J95" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K95" s="16"/>
@@ -3581,11 +3600,11 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
       <c r="I96" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J96" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K96" s="16"/>
@@ -3603,11 +3622,11 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
       <c r="I97" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J97" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K97" s="16"/>
@@ -3625,11 +3644,11 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
       <c r="I98" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J98" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K98" s="16"/>
@@ -3647,11 +3666,11 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
       <c r="I99" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J99" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K99" s="16"/>
@@ -3669,11 +3688,11 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
       <c r="I100" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J100" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K100" s="16"/>
@@ -3691,11 +3710,11 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
       <c r="I101" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J101" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K101" s="16"/>
@@ -3713,11 +3732,11 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
       <c r="I102" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J102" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K102" s="16"/>
@@ -3735,11 +3754,11 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
       <c r="I103" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J103" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K103" s="16"/>
@@ -3757,11 +3776,11 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
       <c r="I104" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J104" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K104" s="16"/>
@@ -3779,11 +3798,11 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
       <c r="I105" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J105" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K105" s="16"/>
@@ -3801,11 +3820,11 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
       <c r="I106" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J106" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K106" s="16"/>
@@ -3823,11 +3842,11 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
       <c r="I107" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J107" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K107" s="16"/>
@@ -3845,11 +3864,11 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
       <c r="I108" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J108" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K108" s="16"/>
@@ -3867,11 +3886,11 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
       <c r="I109" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J109" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K109" s="16"/>
@@ -3889,11 +3908,11 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
       <c r="I110" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J110" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K110" s="16"/>
@@ -3911,11 +3930,11 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
       <c r="I111" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J111" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K111" s="16"/>
@@ -3933,11 +3952,11 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
       <c r="I112" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J112" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K112" s="16"/>
@@ -3955,11 +3974,11 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
       <c r="I113" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J113" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K113" s="16"/>
@@ -3977,11 +3996,11 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
       <c r="I114" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J114" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K114" s="16"/>
@@ -3999,11 +4018,11 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
       <c r="I115" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J115" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K115" s="16"/>
@@ -4021,11 +4040,11 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
       <c r="I116" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J116" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K116" s="16"/>
@@ -4043,11 +4062,11 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
       <c r="I117" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J117" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K117" s="16"/>
@@ -4065,11 +4084,11 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
       <c r="I118" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I118:I181" si="8">IF(SUM(B118:F118,H118)=0,"",SUM(B118:F118,H118))</f>
         <v/>
       </c>
       <c r="J118" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J118:J181" si="9">IF(I118="","",1440-I118)</f>
         <v/>
       </c>
       <c r="K118" s="16"/>
@@ -4087,11 +4106,11 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
       <c r="I119" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J119" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K119" s="16"/>
@@ -4109,11 +4128,11 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
       <c r="I120" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J120" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K120" s="16"/>
@@ -4131,11 +4150,11 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
       <c r="I121" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J121" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K121" s="16"/>
@@ -4153,11 +4172,11 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
       <c r="I122" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J122" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K122" s="16"/>
@@ -4175,11 +4194,11 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
       <c r="I123" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J123" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K123" s="16"/>
@@ -4197,11 +4216,11 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
       <c r="I124" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J124" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K124" s="16"/>
@@ -4219,11 +4238,11 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
       <c r="I125" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J125" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K125" s="16"/>
@@ -4241,11 +4260,11 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
       <c r="I126" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J126" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K126" s="16"/>
@@ -4263,11 +4282,11 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
       <c r="I127" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J127" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K127" s="16"/>
@@ -4285,11 +4304,11 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
       <c r="I128" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J128" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K128" s="16"/>
@@ -4307,11 +4326,11 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
       <c r="I129" s="15" t="str">
-        <f t="shared" ref="I129:I192" si="6">IF(SUM(B129:F129,H129)=0,"",SUM(B129:F129,H129))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J129" s="15" t="str">
-        <f t="shared" ref="J129:J192" si="7">IF(I129="","",1440-I129)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K129" s="16"/>
@@ -4329,11 +4348,11 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
       <c r="I130" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J130" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K130" s="16"/>
@@ -4351,11 +4370,11 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
       <c r="I131" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J131" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K131" s="16"/>
@@ -4373,11 +4392,11 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
       <c r="I132" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J132" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K132" s="16"/>
@@ -4395,11 +4414,11 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
       <c r="I133" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J133" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K133" s="16"/>
@@ -4417,11 +4436,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4439,11 +4458,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4461,11 +4480,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4483,11 +4502,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4505,11 +4524,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -4527,11 +4546,11 @@
       <c r="G139" s="14"/>
       <c r="H139" s="14"/>
       <c r="I139" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J139" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K139" s="16"/>
@@ -4549,11 +4568,11 @@
       <c r="G140" s="14"/>
       <c r="H140" s="14"/>
       <c r="I140" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J140" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K140" s="16"/>
@@ -4571,11 +4590,11 @@
       <c r="G141" s="14"/>
       <c r="H141" s="14"/>
       <c r="I141" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J141" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K141" s="16"/>
@@ -4593,11 +4612,11 @@
       <c r="G142" s="14"/>
       <c r="H142" s="14"/>
       <c r="I142" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J142" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K142" s="16"/>
@@ -4615,11 +4634,11 @@
       <c r="G143" s="14"/>
       <c r="H143" s="14"/>
       <c r="I143" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J143" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K143" s="16"/>
@@ -4637,11 +4656,11 @@
       <c r="G144" s="14"/>
       <c r="H144" s="14"/>
       <c r="I144" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J144" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K144" s="16"/>
@@ -4659,11 +4678,11 @@
       <c r="G145" s="14"/>
       <c r="H145" s="14"/>
       <c r="I145" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J145" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K145" s="16"/>
@@ -4681,11 +4700,11 @@
       <c r="G146" s="14"/>
       <c r="H146" s="14"/>
       <c r="I146" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J146" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K146" s="16"/>
@@ -4703,11 +4722,11 @@
       <c r="G147" s="14"/>
       <c r="H147" s="14"/>
       <c r="I147" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J147" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K147" s="16"/>
@@ -4725,11 +4744,11 @@
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J148" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K148" s="16"/>
@@ -4747,11 +4766,11 @@
       <c r="G149" s="14"/>
       <c r="H149" s="14"/>
       <c r="I149" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J149" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K149" s="16"/>
@@ -4769,11 +4788,11 @@
       <c r="G150" s="14"/>
       <c r="H150" s="14"/>
       <c r="I150" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J150" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K150" s="16"/>
@@ -4791,11 +4810,11 @@
       <c r="G151" s="14"/>
       <c r="H151" s="14"/>
       <c r="I151" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J151" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K151" s="16"/>
@@ -4813,11 +4832,11 @@
       <c r="G152" s="14"/>
       <c r="H152" s="14"/>
       <c r="I152" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J152" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K152" s="16"/>
@@ -4835,11 +4854,11 @@
       <c r="G153" s="14"/>
       <c r="H153" s="14"/>
       <c r="I153" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J153" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K153" s="16"/>
@@ -4857,11 +4876,11 @@
       <c r="G154" s="14"/>
       <c r="H154" s="14"/>
       <c r="I154" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J154" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K154" s="16"/>
@@ -4879,11 +4898,11 @@
       <c r="G155" s="14"/>
       <c r="H155" s="14"/>
       <c r="I155" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J155" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K155" s="16"/>
@@ -4901,11 +4920,11 @@
       <c r="G156" s="14"/>
       <c r="H156" s="14"/>
       <c r="I156" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J156" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K156" s="16"/>
@@ -4923,11 +4942,11 @@
       <c r="G157" s="14"/>
       <c r="H157" s="14"/>
       <c r="I157" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J157" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K157" s="16"/>
@@ -4945,11 +4964,11 @@
       <c r="G158" s="14"/>
       <c r="H158" s="14"/>
       <c r="I158" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J158" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K158" s="16"/>
@@ -4967,11 +4986,11 @@
       <c r="G159" s="14"/>
       <c r="H159" s="14"/>
       <c r="I159" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J159" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K159" s="16"/>
@@ -4989,11 +5008,11 @@
       <c r="G160" s="14"/>
       <c r="H160" s="14"/>
       <c r="I160" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J160" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K160" s="16"/>
@@ -5011,11 +5030,11 @@
       <c r="G161" s="14"/>
       <c r="H161" s="14"/>
       <c r="I161" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J161" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K161" s="16"/>
@@ -5033,11 +5052,11 @@
       <c r="G162" s="14"/>
       <c r="H162" s="14"/>
       <c r="I162" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J162" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K162" s="16"/>
@@ -5055,11 +5074,11 @@
       <c r="G163" s="14"/>
       <c r="H163" s="14"/>
       <c r="I163" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J163" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K163" s="16"/>
@@ -5077,11 +5096,11 @@
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J164" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K164" s="16"/>
@@ -5099,11 +5118,11 @@
       <c r="G165" s="14"/>
       <c r="H165" s="14"/>
       <c r="I165" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J165" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K165" s="16"/>
@@ -5121,11 +5140,11 @@
       <c r="G166" s="14"/>
       <c r="H166" s="14"/>
       <c r="I166" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J166" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K166" s="16"/>
@@ -5143,11 +5162,11 @@
       <c r="G167" s="14"/>
       <c r="H167" s="14"/>
       <c r="I167" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J167" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K167" s="16"/>
@@ -5165,11 +5184,11 @@
       <c r="G168" s="14"/>
       <c r="H168" s="14"/>
       <c r="I168" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J168" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K168" s="16"/>
@@ -5187,11 +5206,11 @@
       <c r="G169" s="14"/>
       <c r="H169" s="14"/>
       <c r="I169" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J169" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K169" s="16"/>
@@ -5209,11 +5228,11 @@
       <c r="G170" s="14"/>
       <c r="H170" s="14"/>
       <c r="I170" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J170" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K170" s="16"/>
@@ -5231,11 +5250,11 @@
       <c r="G171" s="14"/>
       <c r="H171" s="14"/>
       <c r="I171" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J171" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K171" s="16"/>
@@ -5253,11 +5272,11 @@
       <c r="G172" s="14"/>
       <c r="H172" s="14"/>
       <c r="I172" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J172" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K172" s="16"/>
@@ -5275,11 +5294,11 @@
       <c r="G173" s="14"/>
       <c r="H173" s="14"/>
       <c r="I173" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J173" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K173" s="16"/>
@@ -5297,11 +5316,11 @@
       <c r="G174" s="14"/>
       <c r="H174" s="14"/>
       <c r="I174" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J174" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K174" s="16"/>
@@ -5319,11 +5338,11 @@
       <c r="G175" s="14"/>
       <c r="H175" s="14"/>
       <c r="I175" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J175" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K175" s="16"/>
@@ -5341,11 +5360,11 @@
       <c r="G176" s="14"/>
       <c r="H176" s="14"/>
       <c r="I176" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J176" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K176" s="16"/>
@@ -5363,11 +5382,11 @@
       <c r="G177" s="14"/>
       <c r="H177" s="14"/>
       <c r="I177" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J177" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K177" s="16"/>
@@ -5385,11 +5404,11 @@
       <c r="G178" s="14"/>
       <c r="H178" s="14"/>
       <c r="I178" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J178" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K178" s="16"/>
@@ -5407,11 +5426,11 @@
       <c r="G179" s="14"/>
       <c r="H179" s="14"/>
       <c r="I179" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J179" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K179" s="16"/>
@@ -5429,11 +5448,11 @@
       <c r="G180" s="14"/>
       <c r="H180" s="14"/>
       <c r="I180" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J180" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K180" s="16"/>
@@ -5451,11 +5470,11 @@
       <c r="G181" s="14"/>
       <c r="H181" s="14"/>
       <c r="I181" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J181" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K181" s="16"/>
@@ -5473,11 +5492,11 @@
       <c r="G182" s="14"/>
       <c r="H182" s="14"/>
       <c r="I182" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I182:I245" si="10">IF(SUM(B182:F182,H182)=0,"",SUM(B182:F182,H182))</f>
         <v/>
       </c>
       <c r="J182" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J182:J245" si="11">IF(I182="","",1440-I182)</f>
         <v/>
       </c>
       <c r="K182" s="16"/>
@@ -5495,11 +5514,11 @@
       <c r="G183" s="14"/>
       <c r="H183" s="14"/>
       <c r="I183" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J183" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K183" s="16"/>
@@ -5517,11 +5536,11 @@
       <c r="G184" s="14"/>
       <c r="H184" s="14"/>
       <c r="I184" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J184" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K184" s="16"/>
@@ -5539,11 +5558,11 @@
       <c r="G185" s="14"/>
       <c r="H185" s="14"/>
       <c r="I185" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J185" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K185" s="16"/>
@@ -5561,11 +5580,11 @@
       <c r="G186" s="14"/>
       <c r="H186" s="14"/>
       <c r="I186" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J186" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K186" s="16"/>
@@ -5583,11 +5602,11 @@
       <c r="G187" s="14"/>
       <c r="H187" s="14"/>
       <c r="I187" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J187" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K187" s="16"/>
@@ -5605,11 +5624,11 @@
       <c r="G188" s="14"/>
       <c r="H188" s="14"/>
       <c r="I188" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J188" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K188" s="16"/>
@@ -5627,11 +5646,11 @@
       <c r="G189" s="14"/>
       <c r="H189" s="14"/>
       <c r="I189" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J189" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K189" s="16"/>
@@ -5649,11 +5668,11 @@
       <c r="G190" s="14"/>
       <c r="H190" s="14"/>
       <c r="I190" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J190" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K190" s="16"/>
@@ -5671,11 +5690,11 @@
       <c r="G191" s="14"/>
       <c r="H191" s="14"/>
       <c r="I191" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J191" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K191" s="16"/>
@@ -5693,11 +5712,11 @@
       <c r="G192" s="14"/>
       <c r="H192" s="14"/>
       <c r="I192" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J192" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K192" s="16"/>
@@ -5715,11 +5734,11 @@
       <c r="G193" s="14"/>
       <c r="H193" s="14"/>
       <c r="I193" s="15" t="str">
-        <f t="shared" ref="I193:I256" si="8">IF(SUM(B193:F193,H193)=0,"",SUM(B193:F193,H193))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J193" s="15" t="str">
-        <f t="shared" ref="J193:J256" si="9">IF(I193="","",1440-I193)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K193" s="16"/>
@@ -5737,11 +5756,11 @@
       <c r="G194" s="14"/>
       <c r="H194" s="14"/>
       <c r="I194" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J194" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K194" s="16"/>
@@ -5759,11 +5778,11 @@
       <c r="G195" s="14"/>
       <c r="H195" s="14"/>
       <c r="I195" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J195" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K195" s="16"/>
@@ -5781,11 +5800,11 @@
       <c r="G196" s="14"/>
       <c r="H196" s="14"/>
       <c r="I196" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J196" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K196" s="16"/>
@@ -5803,11 +5822,11 @@
       <c r="G197" s="14"/>
       <c r="H197" s="14"/>
       <c r="I197" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J197" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K197" s="16"/>
@@ -5825,11 +5844,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -5847,11 +5866,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -5869,11 +5888,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -5891,11 +5910,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -5913,11 +5932,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -5935,11 +5954,11 @@
       <c r="G203" s="14"/>
       <c r="H203" s="14"/>
       <c r="I203" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J203" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K203" s="16"/>
@@ -5957,11 +5976,11 @@
       <c r="G204" s="14"/>
       <c r="H204" s="14"/>
       <c r="I204" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J204" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K204" s="16"/>
@@ -5979,11 +5998,11 @@
       <c r="G205" s="14"/>
       <c r="H205" s="14"/>
       <c r="I205" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J205" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K205" s="16"/>
@@ -6001,11 +6020,11 @@
       <c r="G206" s="14"/>
       <c r="H206" s="14"/>
       <c r="I206" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J206" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K206" s="16"/>
@@ -6023,11 +6042,11 @@
       <c r="G207" s="14"/>
       <c r="H207" s="14"/>
       <c r="I207" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J207" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K207" s="16"/>
@@ -6045,11 +6064,11 @@
       <c r="G208" s="14"/>
       <c r="H208" s="14"/>
       <c r="I208" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J208" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K208" s="16"/>
@@ -6067,11 +6086,11 @@
       <c r="G209" s="14"/>
       <c r="H209" s="14"/>
       <c r="I209" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J209" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K209" s="16"/>
@@ -6089,11 +6108,11 @@
       <c r="G210" s="14"/>
       <c r="H210" s="14"/>
       <c r="I210" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J210" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K210" s="16"/>
@@ -6111,11 +6130,11 @@
       <c r="G211" s="14"/>
       <c r="H211" s="14"/>
       <c r="I211" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J211" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K211" s="16"/>
@@ -6133,11 +6152,11 @@
       <c r="G212" s="14"/>
       <c r="H212" s="14"/>
       <c r="I212" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J212" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K212" s="16"/>
@@ -6155,11 +6174,11 @@
       <c r="G213" s="14"/>
       <c r="H213" s="14"/>
       <c r="I213" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J213" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K213" s="16"/>
@@ -6177,11 +6196,11 @@
       <c r="G214" s="14"/>
       <c r="H214" s="14"/>
       <c r="I214" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J214" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K214" s="16"/>
@@ -6199,11 +6218,11 @@
       <c r="G215" s="14"/>
       <c r="H215" s="14"/>
       <c r="I215" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J215" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K215" s="16"/>
@@ -6221,11 +6240,11 @@
       <c r="G216" s="14"/>
       <c r="H216" s="14"/>
       <c r="I216" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J216" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K216" s="16"/>
@@ -6243,11 +6262,11 @@
       <c r="G217" s="14"/>
       <c r="H217" s="14"/>
       <c r="I217" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J217" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K217" s="16"/>
@@ -6265,11 +6284,11 @@
       <c r="G218" s="14"/>
       <c r="H218" s="14"/>
       <c r="I218" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J218" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K218" s="16"/>
@@ -6287,11 +6306,11 @@
       <c r="G219" s="14"/>
       <c r="H219" s="14"/>
       <c r="I219" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J219" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K219" s="16"/>
@@ -6309,11 +6328,11 @@
       <c r="G220" s="14"/>
       <c r="H220" s="14"/>
       <c r="I220" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J220" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K220" s="16"/>
@@ -6331,11 +6350,11 @@
       <c r="G221" s="14"/>
       <c r="H221" s="14"/>
       <c r="I221" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J221" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K221" s="16"/>
@@ -6353,11 +6372,11 @@
       <c r="G222" s="14"/>
       <c r="H222" s="14"/>
       <c r="I222" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J222" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K222" s="16"/>
@@ -6375,11 +6394,11 @@
       <c r="G223" s="14"/>
       <c r="H223" s="14"/>
       <c r="I223" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J223" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K223" s="16"/>
@@ -6397,11 +6416,11 @@
       <c r="G224" s="14"/>
       <c r="H224" s="14"/>
       <c r="I224" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J224" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K224" s="16"/>
@@ -6419,11 +6438,11 @@
       <c r="G225" s="14"/>
       <c r="H225" s="14"/>
       <c r="I225" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J225" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K225" s="16"/>
@@ -6441,11 +6460,11 @@
       <c r="G226" s="14"/>
       <c r="H226" s="14"/>
       <c r="I226" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J226" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K226" s="16"/>
@@ -6463,11 +6482,11 @@
       <c r="G227" s="14"/>
       <c r="H227" s="14"/>
       <c r="I227" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J227" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K227" s="16"/>
@@ -6485,11 +6504,11 @@
       <c r="G228" s="14"/>
       <c r="H228" s="14"/>
       <c r="I228" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J228" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K228" s="16"/>
@@ -6507,11 +6526,11 @@
       <c r="G229" s="14"/>
       <c r="H229" s="14"/>
       <c r="I229" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J229" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K229" s="16"/>
@@ -6529,11 +6548,11 @@
       <c r="G230" s="14"/>
       <c r="H230" s="14"/>
       <c r="I230" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J230" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K230" s="16"/>
@@ -6551,11 +6570,11 @@
       <c r="G231" s="14"/>
       <c r="H231" s="14"/>
       <c r="I231" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J231" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K231" s="16"/>
@@ -6573,11 +6592,11 @@
       <c r="G232" s="14"/>
       <c r="H232" s="14"/>
       <c r="I232" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J232" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K232" s="16"/>
@@ -6595,11 +6614,11 @@
       <c r="G233" s="14"/>
       <c r="H233" s="14"/>
       <c r="I233" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J233" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K233" s="16"/>
@@ -6617,11 +6636,11 @@
       <c r="G234" s="14"/>
       <c r="H234" s="14"/>
       <c r="I234" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J234" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K234" s="16"/>
@@ -6639,11 +6658,11 @@
       <c r="G235" s="14"/>
       <c r="H235" s="14"/>
       <c r="I235" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J235" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K235" s="16"/>
@@ -6661,11 +6680,11 @@
       <c r="G236" s="14"/>
       <c r="H236" s="14"/>
       <c r="I236" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J236" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K236" s="16"/>
@@ -6683,11 +6702,11 @@
       <c r="G237" s="14"/>
       <c r="H237" s="14"/>
       <c r="I237" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J237" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K237" s="16"/>
@@ -6705,11 +6724,11 @@
       <c r="G238" s="14"/>
       <c r="H238" s="14"/>
       <c r="I238" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J238" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K238" s="16"/>
@@ -6727,11 +6746,11 @@
       <c r="G239" s="14"/>
       <c r="H239" s="14"/>
       <c r="I239" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J239" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K239" s="16"/>
@@ -6749,11 +6768,11 @@
       <c r="G240" s="14"/>
       <c r="H240" s="14"/>
       <c r="I240" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J240" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K240" s="16"/>
@@ -6771,11 +6790,11 @@
       <c r="G241" s="14"/>
       <c r="H241" s="14"/>
       <c r="I241" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J241" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K241" s="16"/>
@@ -6793,11 +6812,11 @@
       <c r="G242" s="14"/>
       <c r="H242" s="14"/>
       <c r="I242" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J242" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K242" s="16"/>
@@ -6815,11 +6834,11 @@
       <c r="G243" s="14"/>
       <c r="H243" s="14"/>
       <c r="I243" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J243" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K243" s="16"/>
@@ -6837,11 +6856,11 @@
       <c r="G244" s="14"/>
       <c r="H244" s="14"/>
       <c r="I244" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J244" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K244" s="16"/>
@@ -6859,11 +6878,11 @@
       <c r="G245" s="14"/>
       <c r="H245" s="14"/>
       <c r="I245" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J245" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K245" s="16"/>
@@ -6881,11 +6900,11 @@
       <c r="G246" s="14"/>
       <c r="H246" s="14"/>
       <c r="I246" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I246:I309" si="12">IF(SUM(B246:F246,H246)=0,"",SUM(B246:F246,H246))</f>
         <v/>
       </c>
       <c r="J246" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J246:J309" si="13">IF(I246="","",1440-I246)</f>
         <v/>
       </c>
       <c r="K246" s="16"/>
@@ -6903,11 +6922,11 @@
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
       <c r="I247" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J247" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K247" s="16"/>
@@ -6925,11 +6944,11 @@
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
       <c r="I248" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J248" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K248" s="16"/>
@@ -6947,11 +6966,11 @@
       <c r="G249" s="14"/>
       <c r="H249" s="14"/>
       <c r="I249" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J249" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K249" s="16"/>
@@ -6969,11 +6988,11 @@
       <c r="G250" s="14"/>
       <c r="H250" s="14"/>
       <c r="I250" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J250" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K250" s="16"/>
@@ -6991,11 +7010,11 @@
       <c r="G251" s="14"/>
       <c r="H251" s="14"/>
       <c r="I251" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J251" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K251" s="16"/>
@@ -7013,11 +7032,11 @@
       <c r="G252" s="14"/>
       <c r="H252" s="14"/>
       <c r="I252" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J252" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K252" s="16"/>
@@ -7035,11 +7054,11 @@
       <c r="G253" s="14"/>
       <c r="H253" s="14"/>
       <c r="I253" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J253" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K253" s="16"/>
@@ -7057,11 +7076,11 @@
       <c r="G254" s="14"/>
       <c r="H254" s="14"/>
       <c r="I254" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J254" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K254" s="16"/>
@@ -7079,11 +7098,11 @@
       <c r="G255" s="14"/>
       <c r="H255" s="14"/>
       <c r="I255" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J255" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K255" s="16"/>
@@ -7101,11 +7120,11 @@
       <c r="G256" s="14"/>
       <c r="H256" s="14"/>
       <c r="I256" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J256" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K256" s="16"/>
@@ -7123,11 +7142,11 @@
       <c r="G257" s="14"/>
       <c r="H257" s="14"/>
       <c r="I257" s="15" t="str">
-        <f t="shared" ref="I257:I320" si="10">IF(SUM(B257:F257,H257)=0,"",SUM(B257:F257,H257))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J257" s="15" t="str">
-        <f t="shared" ref="J257:J320" si="11">IF(I257="","",1440-I257)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K257" s="16"/>
@@ -7145,11 +7164,11 @@
       <c r="G258" s="14"/>
       <c r="H258" s="14"/>
       <c r="I258" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J258" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K258" s="16"/>
@@ -7167,11 +7186,11 @@
       <c r="G259" s="14"/>
       <c r="H259" s="14"/>
       <c r="I259" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J259" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K259" s="16"/>
@@ -7189,11 +7208,11 @@
       <c r="G260" s="14"/>
       <c r="H260" s="14"/>
       <c r="I260" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J260" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K260" s="16"/>
@@ -7211,11 +7230,11 @@
       <c r="G261" s="14"/>
       <c r="H261" s="14"/>
       <c r="I261" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J261" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K261" s="16"/>
@@ -7233,11 +7252,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7255,11 +7274,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7277,11 +7296,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7299,11 +7318,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7321,11 +7340,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -7343,11 +7362,11 @@
       <c r="G267" s="14"/>
       <c r="H267" s="14"/>
       <c r="I267" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J267" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K267" s="16"/>
@@ -7365,11 +7384,11 @@
       <c r="G268" s="14"/>
       <c r="H268" s="14"/>
       <c r="I268" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J268" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K268" s="16"/>
@@ -7387,11 +7406,11 @@
       <c r="G269" s="14"/>
       <c r="H269" s="14"/>
       <c r="I269" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J269" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K269" s="16"/>
@@ -7409,11 +7428,11 @@
       <c r="G270" s="14"/>
       <c r="H270" s="14"/>
       <c r="I270" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J270" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K270" s="16"/>
@@ -7431,11 +7450,11 @@
       <c r="G271" s="14"/>
       <c r="H271" s="14"/>
       <c r="I271" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J271" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K271" s="16"/>
@@ -7453,11 +7472,11 @@
       <c r="G272" s="14"/>
       <c r="H272" s="14"/>
       <c r="I272" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J272" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K272" s="16"/>
@@ -7475,11 +7494,11 @@
       <c r="G273" s="14"/>
       <c r="H273" s="14"/>
       <c r="I273" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J273" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K273" s="16"/>
@@ -7497,11 +7516,11 @@
       <c r="G274" s="14"/>
       <c r="H274" s="14"/>
       <c r="I274" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J274" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K274" s="16"/>
@@ -7519,11 +7538,11 @@
       <c r="G275" s="14"/>
       <c r="H275" s="14"/>
       <c r="I275" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J275" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K275" s="16"/>
@@ -7541,11 +7560,11 @@
       <c r="G276" s="14"/>
       <c r="H276" s="14"/>
       <c r="I276" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J276" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K276" s="16"/>
@@ -7563,11 +7582,11 @@
       <c r="G277" s="14"/>
       <c r="H277" s="14"/>
       <c r="I277" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J277" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K277" s="16"/>
@@ -7585,11 +7604,11 @@
       <c r="G278" s="14"/>
       <c r="H278" s="14"/>
       <c r="I278" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J278" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K278" s="16"/>
@@ -7607,11 +7626,11 @@
       <c r="G279" s="14"/>
       <c r="H279" s="14"/>
       <c r="I279" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J279" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K279" s="16"/>
@@ -7629,11 +7648,11 @@
       <c r="G280" s="14"/>
       <c r="H280" s="14"/>
       <c r="I280" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J280" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K280" s="16"/>
@@ -7651,11 +7670,11 @@
       <c r="G281" s="14"/>
       <c r="H281" s="14"/>
       <c r="I281" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J281" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K281" s="16"/>
@@ -7673,11 +7692,11 @@
       <c r="G282" s="14"/>
       <c r="H282" s="14"/>
       <c r="I282" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J282" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K282" s="16"/>
@@ -7695,11 +7714,11 @@
       <c r="G283" s="14"/>
       <c r="H283" s="14"/>
       <c r="I283" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J283" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K283" s="16"/>
@@ -7717,11 +7736,11 @@
       <c r="G284" s="14"/>
       <c r="H284" s="14"/>
       <c r="I284" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J284" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K284" s="16"/>
@@ -7739,11 +7758,11 @@
       <c r="G285" s="14"/>
       <c r="H285" s="14"/>
       <c r="I285" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J285" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K285" s="16"/>
@@ -7761,11 +7780,11 @@
       <c r="G286" s="14"/>
       <c r="H286" s="14"/>
       <c r="I286" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J286" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K286" s="16"/>
@@ -7783,11 +7802,11 @@
       <c r="G287" s="14"/>
       <c r="H287" s="14"/>
       <c r="I287" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J287" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K287" s="16"/>
@@ -7805,11 +7824,11 @@
       <c r="G288" s="14"/>
       <c r="H288" s="14"/>
       <c r="I288" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J288" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K288" s="16"/>
@@ -7827,11 +7846,11 @@
       <c r="G289" s="14"/>
       <c r="H289" s="14"/>
       <c r="I289" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J289" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K289" s="16"/>
@@ -7849,11 +7868,11 @@
       <c r="G290" s="14"/>
       <c r="H290" s="14"/>
       <c r="I290" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J290" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K290" s="16"/>
@@ -7871,11 +7890,11 @@
       <c r="G291" s="14"/>
       <c r="H291" s="14"/>
       <c r="I291" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J291" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K291" s="16"/>
@@ -7893,11 +7912,11 @@
       <c r="G292" s="14"/>
       <c r="H292" s="14"/>
       <c r="I292" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J292" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K292" s="16"/>
@@ -7915,11 +7934,11 @@
       <c r="G293" s="14"/>
       <c r="H293" s="14"/>
       <c r="I293" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J293" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K293" s="16"/>
@@ -7937,11 +7956,11 @@
       <c r="G294" s="14"/>
       <c r="H294" s="14"/>
       <c r="I294" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J294" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K294" s="16"/>
@@ -7959,11 +7978,11 @@
       <c r="G295" s="14"/>
       <c r="H295" s="14"/>
       <c r="I295" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J295" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K295" s="16"/>
@@ -7981,11 +8000,11 @@
       <c r="G296" s="14"/>
       <c r="H296" s="14"/>
       <c r="I296" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J296" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K296" s="16"/>
@@ -8003,11 +8022,11 @@
       <c r="G297" s="14"/>
       <c r="H297" s="14"/>
       <c r="I297" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J297" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K297" s="16"/>
@@ -8025,11 +8044,11 @@
       <c r="G298" s="14"/>
       <c r="H298" s="14"/>
       <c r="I298" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J298" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K298" s="16"/>
@@ -8047,11 +8066,11 @@
       <c r="G299" s="14"/>
       <c r="H299" s="14"/>
       <c r="I299" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J299" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K299" s="16"/>
@@ -8069,11 +8088,11 @@
       <c r="G300" s="14"/>
       <c r="H300" s="14"/>
       <c r="I300" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J300" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K300" s="16"/>
@@ -8091,11 +8110,11 @@
       <c r="G301" s="14"/>
       <c r="H301" s="14"/>
       <c r="I301" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J301" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K301" s="16"/>
@@ -8113,11 +8132,11 @@
       <c r="G302" s="14"/>
       <c r="H302" s="14"/>
       <c r="I302" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J302" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K302" s="16"/>
@@ -8135,11 +8154,11 @@
       <c r="G303" s="14"/>
       <c r="H303" s="14"/>
       <c r="I303" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J303" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K303" s="16"/>
@@ -8157,11 +8176,11 @@
       <c r="G304" s="14"/>
       <c r="H304" s="14"/>
       <c r="I304" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J304" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K304" s="16"/>
@@ -8179,11 +8198,11 @@
       <c r="G305" s="14"/>
       <c r="H305" s="14"/>
       <c r="I305" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J305" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K305" s="16"/>
@@ -8201,11 +8220,11 @@
       <c r="G306" s="14"/>
       <c r="H306" s="14"/>
       <c r="I306" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J306" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K306" s="16"/>
@@ -8223,11 +8242,11 @@
       <c r="G307" s="14"/>
       <c r="H307" s="14"/>
       <c r="I307" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J307" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K307" s="16"/>
@@ -8245,11 +8264,11 @@
       <c r="G308" s="14"/>
       <c r="H308" s="14"/>
       <c r="I308" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J308" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K308" s="16"/>
@@ -8267,11 +8286,11 @@
       <c r="G309" s="14"/>
       <c r="H309" s="14"/>
       <c r="I309" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J309" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K309" s="16"/>
@@ -8289,11 +8308,11 @@
       <c r="G310" s="14"/>
       <c r="H310" s="14"/>
       <c r="I310" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I310:I321" si="14">IF(SUM(B310:F310,H310)=0,"",SUM(B310:F310,H310))</f>
         <v/>
       </c>
       <c r="J310" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J310:J321" si="15">IF(I310="","",1440-I310)</f>
         <v/>
       </c>
       <c r="K310" s="16"/>
@@ -8311,11 +8330,11 @@
       <c r="G311" s="14"/>
       <c r="H311" s="14"/>
       <c r="I311" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J311" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K311" s="16"/>
@@ -8333,11 +8352,11 @@
       <c r="G312" s="14"/>
       <c r="H312" s="14"/>
       <c r="I312" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J312" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K312" s="16"/>
@@ -8355,11 +8374,11 @@
       <c r="G313" s="14"/>
       <c r="H313" s="14"/>
       <c r="I313" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J313" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K313" s="16"/>
@@ -8377,11 +8396,11 @@
       <c r="G314" s="14"/>
       <c r="H314" s="14"/>
       <c r="I314" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J314" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K314" s="16"/>
@@ -8399,11 +8418,11 @@
       <c r="G315" s="14"/>
       <c r="H315" s="14"/>
       <c r="I315" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J315" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K315" s="16"/>
@@ -8421,11 +8440,11 @@
       <c r="G316" s="14"/>
       <c r="H316" s="14"/>
       <c r="I316" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J316" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K316" s="16"/>
@@ -8443,11 +8462,11 @@
       <c r="G317" s="14"/>
       <c r="H317" s="14"/>
       <c r="I317" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J317" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K317" s="16"/>
@@ -8465,11 +8484,11 @@
       <c r="G318" s="14"/>
       <c r="H318" s="14"/>
       <c r="I318" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J318" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K318" s="16"/>
@@ -8487,11 +8506,11 @@
       <c r="G319" s="14"/>
       <c r="H319" s="14"/>
       <c r="I319" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J319" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K319" s="16"/>
@@ -8509,11 +8528,11 @@
       <c r="G320" s="14"/>
       <c r="H320" s="14"/>
       <c r="I320" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J320" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K320" s="16"/>
@@ -8531,1667 +8550,17 @@
       <c r="G321" s="14"/>
       <c r="H321" s="14"/>
       <c r="I321" s="15" t="str">
-        <f t="shared" ref="I321:I384" si="12">IF(SUM(B321:F321,H321)=0,"",SUM(B321:F321,H321))</f>
+        <f t="shared" si="14"/>
         <v/>
       </c>
       <c r="J321" s="15" t="str">
-        <f t="shared" ref="J321:J384" si="13">IF(I321="","",1440-I321)</f>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="K321" s="16"/>
       <c r="L321" s="16"/>
       <c r="M321" s="16"/>
       <c r="N321" s="17"/>
-    </row>
-    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A322" s="13"/>
-      <c r="B322" s="14"/>
-      <c r="C322" s="14"/>
-      <c r="D322" s="14"/>
-      <c r="E322" s="14"/>
-      <c r="F322" s="14"/>
-      <c r="G322" s="14"/>
-      <c r="H322" s="14"/>
-      <c r="I322" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J322" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K322" s="16"/>
-      <c r="L322" s="16"/>
-      <c r="M322" s="16"/>
-      <c r="N322" s="17"/>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A323" s="13"/>
-      <c r="B323" s="14"/>
-      <c r="C323" s="14"/>
-      <c r="D323" s="14"/>
-      <c r="E323" s="14"/>
-      <c r="F323" s="14"/>
-      <c r="G323" s="14"/>
-      <c r="H323" s="14"/>
-      <c r="I323" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J323" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K323" s="16"/>
-      <c r="L323" s="16"/>
-      <c r="M323" s="16"/>
-      <c r="N323" s="17"/>
-    </row>
-    <row r="324" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A324" s="13"/>
-      <c r="B324" s="14"/>
-      <c r="C324" s="14"/>
-      <c r="D324" s="14"/>
-      <c r="E324" s="14"/>
-      <c r="F324" s="14"/>
-      <c r="G324" s="14"/>
-      <c r="H324" s="14"/>
-      <c r="I324" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J324" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K324" s="16"/>
-      <c r="L324" s="16"/>
-      <c r="M324" s="16"/>
-      <c r="N324" s="17"/>
-    </row>
-    <row r="325" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A325" s="13"/>
-      <c r="B325" s="14"/>
-      <c r="C325" s="14"/>
-      <c r="D325" s="14"/>
-      <c r="E325" s="14"/>
-      <c r="F325" s="14"/>
-      <c r="G325" s="14"/>
-      <c r="H325" s="14"/>
-      <c r="I325" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J325" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K325" s="16"/>
-      <c r="L325" s="16"/>
-      <c r="M325" s="16"/>
-      <c r="N325" s="17"/>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A326" s="13"/>
-      <c r="B326" s="14"/>
-      <c r="C326" s="14"/>
-      <c r="D326" s="14"/>
-      <c r="E326" s="14"/>
-      <c r="F326" s="14"/>
-      <c r="G326" s="14"/>
-      <c r="H326" s="14"/>
-      <c r="I326" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J326" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K326" s="16"/>
-      <c r="L326" s="16"/>
-      <c r="M326" s="16"/>
-      <c r="N326" s="17"/>
-    </row>
-    <row r="327" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A327" s="13"/>
-      <c r="B327" s="14"/>
-      <c r="C327" s="14"/>
-      <c r="D327" s="14"/>
-      <c r="E327" s="14"/>
-      <c r="F327" s="14"/>
-      <c r="G327" s="14"/>
-      <c r="H327" s="14"/>
-      <c r="I327" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J327" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K327" s="16"/>
-      <c r="L327" s="16"/>
-      <c r="M327" s="16"/>
-      <c r="N327" s="17"/>
-    </row>
-    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A328" s="13"/>
-      <c r="B328" s="14"/>
-      <c r="C328" s="14"/>
-      <c r="D328" s="14"/>
-      <c r="E328" s="14"/>
-      <c r="F328" s="14"/>
-      <c r="G328" s="14"/>
-      <c r="H328" s="14"/>
-      <c r="I328" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J328" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K328" s="16"/>
-      <c r="L328" s="16"/>
-      <c r="M328" s="16"/>
-      <c r="N328" s="17"/>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A329" s="13"/>
-      <c r="B329" s="14"/>
-      <c r="C329" s="14"/>
-      <c r="D329" s="14"/>
-      <c r="E329" s="14"/>
-      <c r="F329" s="14"/>
-      <c r="G329" s="14"/>
-      <c r="H329" s="14"/>
-      <c r="I329" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J329" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K329" s="16"/>
-      <c r="L329" s="16"/>
-      <c r="M329" s="16"/>
-      <c r="N329" s="17"/>
-    </row>
-    <row r="330" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A330" s="13"/>
-      <c r="B330" s="14"/>
-      <c r="C330" s="14"/>
-      <c r="D330" s="14"/>
-      <c r="E330" s="14"/>
-      <c r="F330" s="14"/>
-      <c r="G330" s="14"/>
-      <c r="H330" s="14"/>
-      <c r="I330" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J330" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K330" s="16"/>
-      <c r="L330" s="16"/>
-      <c r="M330" s="16"/>
-      <c r="N330" s="17"/>
-    </row>
-    <row r="331" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A331" s="13"/>
-      <c r="B331" s="14"/>
-      <c r="C331" s="14"/>
-      <c r="D331" s="14"/>
-      <c r="E331" s="14"/>
-      <c r="F331" s="14"/>
-      <c r="G331" s="14"/>
-      <c r="H331" s="14"/>
-      <c r="I331" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J331" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K331" s="16"/>
-      <c r="L331" s="16"/>
-      <c r="M331" s="16"/>
-      <c r="N331" s="17"/>
-    </row>
-    <row r="332" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A332" s="13"/>
-      <c r="B332" s="14"/>
-      <c r="C332" s="14"/>
-      <c r="D332" s="14"/>
-      <c r="E332" s="14"/>
-      <c r="F332" s="14"/>
-      <c r="G332" s="14"/>
-      <c r="H332" s="14"/>
-      <c r="I332" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J332" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K332" s="16"/>
-      <c r="L332" s="16"/>
-      <c r="M332" s="16"/>
-      <c r="N332" s="17"/>
-    </row>
-    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A333" s="13"/>
-      <c r="B333" s="14"/>
-      <c r="C333" s="14"/>
-      <c r="D333" s="14"/>
-      <c r="E333" s="14"/>
-      <c r="F333" s="14"/>
-      <c r="G333" s="14"/>
-      <c r="H333" s="14"/>
-      <c r="I333" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J333" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K333" s="16"/>
-      <c r="L333" s="16"/>
-      <c r="M333" s="16"/>
-      <c r="N333" s="17"/>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" s="13"/>
-      <c r="B334" s="14"/>
-      <c r="C334" s="14"/>
-      <c r="D334" s="14"/>
-      <c r="E334" s="14"/>
-      <c r="F334" s="14"/>
-      <c r="G334" s="14"/>
-      <c r="H334" s="14"/>
-      <c r="I334" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J334" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K334" s="16"/>
-      <c r="L334" s="16"/>
-      <c r="M334" s="16"/>
-      <c r="N334" s="17"/>
-    </row>
-    <row r="335" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A335" s="13"/>
-      <c r="B335" s="14"/>
-      <c r="C335" s="14"/>
-      <c r="D335" s="14"/>
-      <c r="E335" s="14"/>
-      <c r="F335" s="14"/>
-      <c r="G335" s="14"/>
-      <c r="H335" s="14"/>
-      <c r="I335" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J335" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K335" s="16"/>
-      <c r="L335" s="16"/>
-      <c r="M335" s="16"/>
-      <c r="N335" s="17"/>
-    </row>
-    <row r="336" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A336" s="13"/>
-      <c r="B336" s="14"/>
-      <c r="C336" s="14"/>
-      <c r="D336" s="14"/>
-      <c r="E336" s="14"/>
-      <c r="F336" s="14"/>
-      <c r="G336" s="14"/>
-      <c r="H336" s="14"/>
-      <c r="I336" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J336" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K336" s="16"/>
-      <c r="L336" s="16"/>
-      <c r="M336" s="16"/>
-      <c r="N336" s="17"/>
-    </row>
-    <row r="337" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A337" s="13"/>
-      <c r="B337" s="14"/>
-      <c r="C337" s="14"/>
-      <c r="D337" s="14"/>
-      <c r="E337" s="14"/>
-      <c r="F337" s="14"/>
-      <c r="G337" s="14"/>
-      <c r="H337" s="14"/>
-      <c r="I337" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J337" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K337" s="16"/>
-      <c r="L337" s="16"/>
-      <c r="M337" s="16"/>
-      <c r="N337" s="17"/>
-    </row>
-    <row r="338" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A338" s="13"/>
-      <c r="B338" s="14"/>
-      <c r="C338" s="14"/>
-      <c r="D338" s="14"/>
-      <c r="E338" s="14"/>
-      <c r="F338" s="14"/>
-      <c r="G338" s="14"/>
-      <c r="H338" s="14"/>
-      <c r="I338" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J338" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K338" s="16"/>
-      <c r="L338" s="16"/>
-      <c r="M338" s="16"/>
-      <c r="N338" s="17"/>
-    </row>
-    <row r="339" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A339" s="13"/>
-      <c r="B339" s="14"/>
-      <c r="C339" s="14"/>
-      <c r="D339" s="14"/>
-      <c r="E339" s="14"/>
-      <c r="F339" s="14"/>
-      <c r="G339" s="14"/>
-      <c r="H339" s="14"/>
-      <c r="I339" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J339" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K339" s="16"/>
-      <c r="L339" s="16"/>
-      <c r="M339" s="16"/>
-      <c r="N339" s="17"/>
-    </row>
-    <row r="340" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A340" s="13"/>
-      <c r="B340" s="14"/>
-      <c r="C340" s="14"/>
-      <c r="D340" s="14"/>
-      <c r="E340" s="14"/>
-      <c r="F340" s="14"/>
-      <c r="G340" s="14"/>
-      <c r="H340" s="14"/>
-      <c r="I340" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J340" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K340" s="16"/>
-      <c r="L340" s="16"/>
-      <c r="M340" s="16"/>
-      <c r="N340" s="17"/>
-    </row>
-    <row r="341" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A341" s="13"/>
-      <c r="B341" s="14"/>
-      <c r="C341" s="14"/>
-      <c r="D341" s="14"/>
-      <c r="E341" s="14"/>
-      <c r="F341" s="14"/>
-      <c r="G341" s="14"/>
-      <c r="H341" s="14"/>
-      <c r="I341" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J341" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K341" s="16"/>
-      <c r="L341" s="16"/>
-      <c r="M341" s="16"/>
-      <c r="N341" s="17"/>
-    </row>
-    <row r="342" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A342" s="13"/>
-      <c r="B342" s="14"/>
-      <c r="C342" s="14"/>
-      <c r="D342" s="14"/>
-      <c r="E342" s="14"/>
-      <c r="F342" s="14"/>
-      <c r="G342" s="14"/>
-      <c r="H342" s="14"/>
-      <c r="I342" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J342" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K342" s="16"/>
-      <c r="L342" s="16"/>
-      <c r="M342" s="16"/>
-      <c r="N342" s="17"/>
-    </row>
-    <row r="343" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A343" s="13"/>
-      <c r="B343" s="14"/>
-      <c r="C343" s="14"/>
-      <c r="D343" s="14"/>
-      <c r="E343" s="14"/>
-      <c r="F343" s="14"/>
-      <c r="G343" s="14"/>
-      <c r="H343" s="14"/>
-      <c r="I343" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J343" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K343" s="16"/>
-      <c r="L343" s="16"/>
-      <c r="M343" s="16"/>
-      <c r="N343" s="17"/>
-    </row>
-    <row r="344" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A344" s="13"/>
-      <c r="B344" s="14"/>
-      <c r="C344" s="14"/>
-      <c r="D344" s="14"/>
-      <c r="E344" s="14"/>
-      <c r="F344" s="14"/>
-      <c r="G344" s="14"/>
-      <c r="H344" s="14"/>
-      <c r="I344" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J344" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K344" s="16"/>
-      <c r="L344" s="16"/>
-      <c r="M344" s="16"/>
-      <c r="N344" s="17"/>
-    </row>
-    <row r="345" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A345" s="13"/>
-      <c r="B345" s="14"/>
-      <c r="C345" s="14"/>
-      <c r="D345" s="14"/>
-      <c r="E345" s="14"/>
-      <c r="F345" s="14"/>
-      <c r="G345" s="14"/>
-      <c r="H345" s="14"/>
-      <c r="I345" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J345" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K345" s="16"/>
-      <c r="L345" s="16"/>
-      <c r="M345" s="16"/>
-      <c r="N345" s="17"/>
-    </row>
-    <row r="346" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A346" s="13"/>
-      <c r="B346" s="14"/>
-      <c r="C346" s="14"/>
-      <c r="D346" s="14"/>
-      <c r="E346" s="14"/>
-      <c r="F346" s="14"/>
-      <c r="G346" s="14"/>
-      <c r="H346" s="14"/>
-      <c r="I346" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J346" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K346" s="16"/>
-      <c r="L346" s="16"/>
-      <c r="M346" s="16"/>
-      <c r="N346" s="17"/>
-    </row>
-    <row r="347" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A347" s="13"/>
-      <c r="B347" s="14"/>
-      <c r="C347" s="14"/>
-      <c r="D347" s="14"/>
-      <c r="E347" s="14"/>
-      <c r="F347" s="14"/>
-      <c r="G347" s="14"/>
-      <c r="H347" s="14"/>
-      <c r="I347" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J347" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K347" s="16"/>
-      <c r="L347" s="16"/>
-      <c r="M347" s="16"/>
-      <c r="N347" s="17"/>
-    </row>
-    <row r="348" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A348" s="13"/>
-      <c r="B348" s="14"/>
-      <c r="C348" s="14"/>
-      <c r="D348" s="14"/>
-      <c r="E348" s="14"/>
-      <c r="F348" s="14"/>
-      <c r="G348" s="14"/>
-      <c r="H348" s="14"/>
-      <c r="I348" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J348" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K348" s="16"/>
-      <c r="L348" s="16"/>
-      <c r="M348" s="16"/>
-      <c r="N348" s="17"/>
-    </row>
-    <row r="349" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A349" s="13"/>
-      <c r="B349" s="14"/>
-      <c r="C349" s="14"/>
-      <c r="D349" s="14"/>
-      <c r="E349" s="14"/>
-      <c r="F349" s="14"/>
-      <c r="G349" s="14"/>
-      <c r="H349" s="14"/>
-      <c r="I349" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J349" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K349" s="16"/>
-      <c r="L349" s="16"/>
-      <c r="M349" s="16"/>
-      <c r="N349" s="17"/>
-    </row>
-    <row r="350" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A350" s="13"/>
-      <c r="B350" s="14"/>
-      <c r="C350" s="14"/>
-      <c r="D350" s="14"/>
-      <c r="E350" s="14"/>
-      <c r="F350" s="14"/>
-      <c r="G350" s="14"/>
-      <c r="H350" s="14"/>
-      <c r="I350" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J350" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K350" s="16"/>
-      <c r="L350" s="16"/>
-      <c r="M350" s="16"/>
-      <c r="N350" s="17"/>
-    </row>
-    <row r="351" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A351" s="13"/>
-      <c r="B351" s="14"/>
-      <c r="C351" s="14"/>
-      <c r="D351" s="14"/>
-      <c r="E351" s="14"/>
-      <c r="F351" s="14"/>
-      <c r="G351" s="14"/>
-      <c r="H351" s="14"/>
-      <c r="I351" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J351" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K351" s="16"/>
-      <c r="L351" s="16"/>
-      <c r="M351" s="16"/>
-      <c r="N351" s="17"/>
-    </row>
-    <row r="352" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A352" s="13"/>
-      <c r="B352" s="14"/>
-      <c r="C352" s="14"/>
-      <c r="D352" s="14"/>
-      <c r="E352" s="14"/>
-      <c r="F352" s="14"/>
-      <c r="G352" s="14"/>
-      <c r="H352" s="14"/>
-      <c r="I352" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J352" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K352" s="16"/>
-      <c r="L352" s="16"/>
-      <c r="M352" s="16"/>
-      <c r="N352" s="17"/>
-    </row>
-    <row r="353" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A353" s="13"/>
-      <c r="B353" s="14"/>
-      <c r="C353" s="14"/>
-      <c r="D353" s="14"/>
-      <c r="E353" s="14"/>
-      <c r="F353" s="14"/>
-      <c r="G353" s="14"/>
-      <c r="H353" s="14"/>
-      <c r="I353" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J353" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K353" s="16"/>
-      <c r="L353" s="16"/>
-      <c r="M353" s="16"/>
-      <c r="N353" s="17"/>
-    </row>
-    <row r="354" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A354" s="13"/>
-      <c r="B354" s="14"/>
-      <c r="C354" s="14"/>
-      <c r="D354" s="14"/>
-      <c r="E354" s="14"/>
-      <c r="F354" s="14"/>
-      <c r="G354" s="14"/>
-      <c r="H354" s="14"/>
-      <c r="I354" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J354" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K354" s="16"/>
-      <c r="L354" s="16"/>
-      <c r="M354" s="16"/>
-      <c r="N354" s="17"/>
-    </row>
-    <row r="355" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A355" s="13"/>
-      <c r="B355" s="14"/>
-      <c r="C355" s="14"/>
-      <c r="D355" s="14"/>
-      <c r="E355" s="14"/>
-      <c r="F355" s="14"/>
-      <c r="G355" s="14"/>
-      <c r="H355" s="14"/>
-      <c r="I355" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J355" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K355" s="16"/>
-      <c r="L355" s="16"/>
-      <c r="M355" s="16"/>
-      <c r="N355" s="17"/>
-    </row>
-    <row r="356" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A356" s="13"/>
-      <c r="B356" s="14"/>
-      <c r="C356" s="14"/>
-      <c r="D356" s="14"/>
-      <c r="E356" s="14"/>
-      <c r="F356" s="14"/>
-      <c r="G356" s="14"/>
-      <c r="H356" s="14"/>
-      <c r="I356" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J356" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K356" s="16"/>
-      <c r="L356" s="16"/>
-      <c r="M356" s="16"/>
-      <c r="N356" s="17"/>
-    </row>
-    <row r="357" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A357" s="13"/>
-      <c r="B357" s="14"/>
-      <c r="C357" s="14"/>
-      <c r="D357" s="14"/>
-      <c r="E357" s="14"/>
-      <c r="F357" s="14"/>
-      <c r="G357" s="14"/>
-      <c r="H357" s="14"/>
-      <c r="I357" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J357" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K357" s="16"/>
-      <c r="L357" s="16"/>
-      <c r="M357" s="16"/>
-      <c r="N357" s="17"/>
-    </row>
-    <row r="358" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A358" s="13"/>
-      <c r="B358" s="14"/>
-      <c r="C358" s="14"/>
-      <c r="D358" s="14"/>
-      <c r="E358" s="14"/>
-      <c r="F358" s="14"/>
-      <c r="G358" s="14"/>
-      <c r="H358" s="14"/>
-      <c r="I358" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J358" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K358" s="16"/>
-      <c r="L358" s="16"/>
-      <c r="M358" s="16"/>
-      <c r="N358" s="17"/>
-    </row>
-    <row r="359" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A359" s="13"/>
-      <c r="B359" s="14"/>
-      <c r="C359" s="14"/>
-      <c r="D359" s="14"/>
-      <c r="E359" s="14"/>
-      <c r="F359" s="14"/>
-      <c r="G359" s="14"/>
-      <c r="H359" s="14"/>
-      <c r="I359" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J359" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K359" s="16"/>
-      <c r="L359" s="16"/>
-      <c r="M359" s="16"/>
-      <c r="N359" s="17"/>
-    </row>
-    <row r="360" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A360" s="13"/>
-      <c r="B360" s="14"/>
-      <c r="C360" s="14"/>
-      <c r="D360" s="14"/>
-      <c r="E360" s="14"/>
-      <c r="F360" s="14"/>
-      <c r="G360" s="14"/>
-      <c r="H360" s="14"/>
-      <c r="I360" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J360" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K360" s="16"/>
-      <c r="L360" s="16"/>
-      <c r="M360" s="16"/>
-      <c r="N360" s="17"/>
-    </row>
-    <row r="361" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A361" s="13"/>
-      <c r="B361" s="14"/>
-      <c r="C361" s="14"/>
-      <c r="D361" s="14"/>
-      <c r="E361" s="14"/>
-      <c r="F361" s="14"/>
-      <c r="G361" s="14"/>
-      <c r="H361" s="14"/>
-      <c r="I361" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J361" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K361" s="16"/>
-      <c r="L361" s="16"/>
-      <c r="M361" s="16"/>
-      <c r="N361" s="17"/>
-    </row>
-    <row r="362" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A362" s="13"/>
-      <c r="B362" s="14"/>
-      <c r="C362" s="14"/>
-      <c r="D362" s="14"/>
-      <c r="E362" s="14"/>
-      <c r="F362" s="14"/>
-      <c r="G362" s="14"/>
-      <c r="H362" s="14"/>
-      <c r="I362" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J362" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K362" s="16"/>
-      <c r="L362" s="16"/>
-      <c r="M362" s="16"/>
-      <c r="N362" s="17"/>
-    </row>
-    <row r="363" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A363" s="13"/>
-      <c r="B363" s="14"/>
-      <c r="C363" s="14"/>
-      <c r="D363" s="14"/>
-      <c r="E363" s="14"/>
-      <c r="F363" s="14"/>
-      <c r="G363" s="14"/>
-      <c r="H363" s="14"/>
-      <c r="I363" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J363" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K363" s="16"/>
-      <c r="L363" s="16"/>
-      <c r="M363" s="16"/>
-      <c r="N363" s="17"/>
-    </row>
-    <row r="364" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A364" s="13"/>
-      <c r="B364" s="14"/>
-      <c r="C364" s="14"/>
-      <c r="D364" s="14"/>
-      <c r="E364" s="14"/>
-      <c r="F364" s="14"/>
-      <c r="G364" s="14"/>
-      <c r="H364" s="14"/>
-      <c r="I364" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J364" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K364" s="16"/>
-      <c r="L364" s="16"/>
-      <c r="M364" s="16"/>
-      <c r="N364" s="17"/>
-    </row>
-    <row r="365" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A365" s="13"/>
-      <c r="B365" s="14"/>
-      <c r="C365" s="14"/>
-      <c r="D365" s="14"/>
-      <c r="E365" s="14"/>
-      <c r="F365" s="14"/>
-      <c r="G365" s="14"/>
-      <c r="H365" s="14"/>
-      <c r="I365" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J365" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K365" s="16"/>
-      <c r="L365" s="16"/>
-      <c r="M365" s="16"/>
-      <c r="N365" s="17"/>
-    </row>
-    <row r="366" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A366" s="13"/>
-      <c r="B366" s="14"/>
-      <c r="C366" s="14"/>
-      <c r="D366" s="14"/>
-      <c r="E366" s="14"/>
-      <c r="F366" s="14"/>
-      <c r="G366" s="14"/>
-      <c r="H366" s="14"/>
-      <c r="I366" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J366" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K366" s="16"/>
-      <c r="L366" s="16"/>
-      <c r="M366" s="16"/>
-      <c r="N366" s="17"/>
-    </row>
-    <row r="367" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A367" s="13"/>
-      <c r="B367" s="14"/>
-      <c r="C367" s="14"/>
-      <c r="D367" s="14"/>
-      <c r="E367" s="14"/>
-      <c r="F367" s="14"/>
-      <c r="G367" s="14"/>
-      <c r="H367" s="14"/>
-      <c r="I367" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J367" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K367" s="16"/>
-      <c r="L367" s="16"/>
-      <c r="M367" s="16"/>
-      <c r="N367" s="17"/>
-    </row>
-    <row r="368" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A368" s="13"/>
-      <c r="B368" s="14"/>
-      <c r="C368" s="14"/>
-      <c r="D368" s="14"/>
-      <c r="E368" s="14"/>
-      <c r="F368" s="14"/>
-      <c r="G368" s="14"/>
-      <c r="H368" s="14"/>
-      <c r="I368" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J368" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K368" s="16"/>
-      <c r="L368" s="16"/>
-      <c r="M368" s="16"/>
-      <c r="N368" s="17"/>
-    </row>
-    <row r="369" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A369" s="13"/>
-      <c r="B369" s="14"/>
-      <c r="C369" s="14"/>
-      <c r="D369" s="14"/>
-      <c r="E369" s="14"/>
-      <c r="F369" s="14"/>
-      <c r="G369" s="14"/>
-      <c r="H369" s="14"/>
-      <c r="I369" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J369" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K369" s="16"/>
-      <c r="L369" s="16"/>
-      <c r="M369" s="16"/>
-      <c r="N369" s="17"/>
-    </row>
-    <row r="370" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A370" s="13"/>
-      <c r="B370" s="14"/>
-      <c r="C370" s="14"/>
-      <c r="D370" s="14"/>
-      <c r="E370" s="14"/>
-      <c r="F370" s="14"/>
-      <c r="G370" s="14"/>
-      <c r="H370" s="14"/>
-      <c r="I370" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J370" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K370" s="16"/>
-      <c r="L370" s="16"/>
-      <c r="M370" s="16"/>
-      <c r="N370" s="17"/>
-    </row>
-    <row r="371" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A371" s="13"/>
-      <c r="B371" s="14"/>
-      <c r="C371" s="14"/>
-      <c r="D371" s="14"/>
-      <c r="E371" s="14"/>
-      <c r="F371" s="14"/>
-      <c r="G371" s="14"/>
-      <c r="H371" s="14"/>
-      <c r="I371" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J371" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K371" s="16"/>
-      <c r="L371" s="16"/>
-      <c r="M371" s="16"/>
-      <c r="N371" s="17"/>
-    </row>
-    <row r="372" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A372" s="13"/>
-      <c r="B372" s="14"/>
-      <c r="C372" s="14"/>
-      <c r="D372" s="14"/>
-      <c r="E372" s="14"/>
-      <c r="F372" s="14"/>
-      <c r="G372" s="14"/>
-      <c r="H372" s="14"/>
-      <c r="I372" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J372" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K372" s="16"/>
-      <c r="L372" s="16"/>
-      <c r="M372" s="16"/>
-      <c r="N372" s="17"/>
-    </row>
-    <row r="373" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A373" s="13"/>
-      <c r="B373" s="14"/>
-      <c r="C373" s="14"/>
-      <c r="D373" s="14"/>
-      <c r="E373" s="14"/>
-      <c r="F373" s="14"/>
-      <c r="G373" s="14"/>
-      <c r="H373" s="14"/>
-      <c r="I373" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J373" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K373" s="16"/>
-      <c r="L373" s="16"/>
-      <c r="M373" s="16"/>
-      <c r="N373" s="17"/>
-    </row>
-    <row r="374" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A374" s="13"/>
-      <c r="B374" s="14"/>
-      <c r="C374" s="14"/>
-      <c r="D374" s="14"/>
-      <c r="E374" s="14"/>
-      <c r="F374" s="14"/>
-      <c r="G374" s="14"/>
-      <c r="H374" s="14"/>
-      <c r="I374" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J374" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K374" s="16"/>
-      <c r="L374" s="16"/>
-      <c r="M374" s="16"/>
-      <c r="N374" s="17"/>
-    </row>
-    <row r="375" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A375" s="13"/>
-      <c r="B375" s="14"/>
-      <c r="C375" s="14"/>
-      <c r="D375" s="14"/>
-      <c r="E375" s="14"/>
-      <c r="F375" s="14"/>
-      <c r="G375" s="14"/>
-      <c r="H375" s="14"/>
-      <c r="I375" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J375" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K375" s="16"/>
-      <c r="L375" s="16"/>
-      <c r="M375" s="16"/>
-      <c r="N375" s="17"/>
-    </row>
-    <row r="376" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A376" s="13"/>
-      <c r="B376" s="14"/>
-      <c r="C376" s="14"/>
-      <c r="D376" s="14"/>
-      <c r="E376" s="14"/>
-      <c r="F376" s="14"/>
-      <c r="G376" s="14"/>
-      <c r="H376" s="14"/>
-      <c r="I376" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J376" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K376" s="16"/>
-      <c r="L376" s="16"/>
-      <c r="M376" s="16"/>
-      <c r="N376" s="17"/>
-    </row>
-    <row r="377" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A377" s="13"/>
-      <c r="B377" s="14"/>
-      <c r="C377" s="14"/>
-      <c r="D377" s="14"/>
-      <c r="E377" s="14"/>
-      <c r="F377" s="14"/>
-      <c r="G377" s="14"/>
-      <c r="H377" s="14"/>
-      <c r="I377" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J377" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K377" s="16"/>
-      <c r="L377" s="16"/>
-      <c r="M377" s="16"/>
-      <c r="N377" s="17"/>
-    </row>
-    <row r="378" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A378" s="13"/>
-      <c r="B378" s="14"/>
-      <c r="C378" s="14"/>
-      <c r="D378" s="14"/>
-      <c r="E378" s="14"/>
-      <c r="F378" s="14"/>
-      <c r="G378" s="14"/>
-      <c r="H378" s="14"/>
-      <c r="I378" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J378" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K378" s="16"/>
-      <c r="L378" s="16"/>
-      <c r="M378" s="16"/>
-      <c r="N378" s="17"/>
-    </row>
-    <row r="379" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A379" s="13"/>
-      <c r="B379" s="14"/>
-      <c r="C379" s="14"/>
-      <c r="D379" s="14"/>
-      <c r="E379" s="14"/>
-      <c r="F379" s="14"/>
-      <c r="G379" s="14"/>
-      <c r="H379" s="14"/>
-      <c r="I379" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J379" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K379" s="16"/>
-      <c r="L379" s="16"/>
-      <c r="M379" s="16"/>
-      <c r="N379" s="17"/>
-    </row>
-    <row r="380" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A380" s="13"/>
-      <c r="B380" s="14"/>
-      <c r="C380" s="14"/>
-      <c r="D380" s="14"/>
-      <c r="E380" s="14"/>
-      <c r="F380" s="14"/>
-      <c r="G380" s="14"/>
-      <c r="H380" s="14"/>
-      <c r="I380" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J380" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K380" s="16"/>
-      <c r="L380" s="16"/>
-      <c r="M380" s="16"/>
-      <c r="N380" s="17"/>
-    </row>
-    <row r="381" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A381" s="13"/>
-      <c r="B381" s="14"/>
-      <c r="C381" s="14"/>
-      <c r="D381" s="14"/>
-      <c r="E381" s="14"/>
-      <c r="F381" s="14"/>
-      <c r="G381" s="14"/>
-      <c r="H381" s="14"/>
-      <c r="I381" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J381" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K381" s="16"/>
-      <c r="L381" s="16"/>
-      <c r="M381" s="16"/>
-      <c r="N381" s="17"/>
-    </row>
-    <row r="382" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A382" s="13"/>
-      <c r="B382" s="14"/>
-      <c r="C382" s="14"/>
-      <c r="D382" s="14"/>
-      <c r="E382" s="14"/>
-      <c r="F382" s="14"/>
-      <c r="G382" s="14"/>
-      <c r="H382" s="14"/>
-      <c r="I382" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J382" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K382" s="16"/>
-      <c r="L382" s="16"/>
-      <c r="M382" s="16"/>
-      <c r="N382" s="17"/>
-    </row>
-    <row r="383" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A383" s="13"/>
-      <c r="B383" s="14"/>
-      <c r="C383" s="14"/>
-      <c r="D383" s="14"/>
-      <c r="E383" s="14"/>
-      <c r="F383" s="14"/>
-      <c r="G383" s="14"/>
-      <c r="H383" s="14"/>
-      <c r="I383" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J383" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K383" s="16"/>
-      <c r="L383" s="16"/>
-      <c r="M383" s="16"/>
-      <c r="N383" s="17"/>
-    </row>
-    <row r="384" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A384" s="13"/>
-      <c r="B384" s="14"/>
-      <c r="C384" s="14"/>
-      <c r="D384" s="14"/>
-      <c r="E384" s="14"/>
-      <c r="F384" s="14"/>
-      <c r="G384" s="14"/>
-      <c r="H384" s="14"/>
-      <c r="I384" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J384" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K384" s="16"/>
-      <c r="L384" s="16"/>
-      <c r="M384" s="16"/>
-      <c r="N384" s="17"/>
-    </row>
-    <row r="385" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A385" s="13"/>
-      <c r="B385" s="14"/>
-      <c r="C385" s="14"/>
-      <c r="D385" s="14"/>
-      <c r="E385" s="14"/>
-      <c r="F385" s="14"/>
-      <c r="G385" s="14"/>
-      <c r="H385" s="14"/>
-      <c r="I385" s="15" t="str">
-        <f t="shared" ref="I385:I396" si="14">IF(SUM(B385:F385,H385)=0,"",SUM(B385:F385,H385))</f>
-        <v/>
-      </c>
-      <c r="J385" s="15" t="str">
-        <f t="shared" ref="J385:J396" si="15">IF(I385="","",1440-I385)</f>
-        <v/>
-      </c>
-      <c r="K385" s="16"/>
-      <c r="L385" s="16"/>
-      <c r="M385" s="16"/>
-      <c r="N385" s="17"/>
-    </row>
-    <row r="386" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A386" s="13"/>
-      <c r="B386" s="14"/>
-      <c r="C386" s="14"/>
-      <c r="D386" s="14"/>
-      <c r="E386" s="14"/>
-      <c r="F386" s="14"/>
-      <c r="G386" s="14"/>
-      <c r="H386" s="14"/>
-      <c r="I386" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J386" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K386" s="16"/>
-      <c r="L386" s="16"/>
-      <c r="M386" s="16"/>
-      <c r="N386" s="17"/>
-    </row>
-    <row r="387" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A387" s="13"/>
-      <c r="B387" s="14"/>
-      <c r="C387" s="14"/>
-      <c r="D387" s="14"/>
-      <c r="E387" s="14"/>
-      <c r="F387" s="14"/>
-      <c r="G387" s="14"/>
-      <c r="H387" s="14"/>
-      <c r="I387" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J387" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K387" s="16"/>
-      <c r="L387" s="16"/>
-      <c r="M387" s="16"/>
-      <c r="N387" s="17"/>
-    </row>
-    <row r="388" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A388" s="13"/>
-      <c r="B388" s="14"/>
-      <c r="C388" s="14"/>
-      <c r="D388" s="14"/>
-      <c r="E388" s="14"/>
-      <c r="F388" s="14"/>
-      <c r="G388" s="14"/>
-      <c r="H388" s="14"/>
-      <c r="I388" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J388" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K388" s="16"/>
-      <c r="L388" s="16"/>
-      <c r="M388" s="16"/>
-      <c r="N388" s="17"/>
-    </row>
-    <row r="389" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A389" s="13"/>
-      <c r="B389" s="14"/>
-      <c r="C389" s="14"/>
-      <c r="D389" s="14"/>
-      <c r="E389" s="14"/>
-      <c r="F389" s="14"/>
-      <c r="G389" s="14"/>
-      <c r="H389" s="14"/>
-      <c r="I389" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J389" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K389" s="16"/>
-      <c r="L389" s="16"/>
-      <c r="M389" s="16"/>
-      <c r="N389" s="17"/>
-    </row>
-    <row r="390" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A390" s="13"/>
-      <c r="B390" s="14"/>
-      <c r="C390" s="14"/>
-      <c r="D390" s="14"/>
-      <c r="E390" s="14"/>
-      <c r="F390" s="14"/>
-      <c r="G390" s="14"/>
-      <c r="H390" s="14"/>
-      <c r="I390" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J390" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K390" s="16"/>
-      <c r="L390" s="16"/>
-      <c r="M390" s="16"/>
-      <c r="N390" s="17"/>
-    </row>
-    <row r="391" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A391" s="13"/>
-      <c r="B391" s="14"/>
-      <c r="C391" s="14"/>
-      <c r="D391" s="14"/>
-      <c r="E391" s="14"/>
-      <c r="F391" s="14"/>
-      <c r="G391" s="14"/>
-      <c r="H391" s="14"/>
-      <c r="I391" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J391" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K391" s="16"/>
-      <c r="L391" s="16"/>
-      <c r="M391" s="16"/>
-      <c r="N391" s="17"/>
-    </row>
-    <row r="392" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A392" s="13"/>
-      <c r="B392" s="14"/>
-      <c r="C392" s="14"/>
-      <c r="D392" s="14"/>
-      <c r="E392" s="14"/>
-      <c r="F392" s="14"/>
-      <c r="G392" s="14"/>
-      <c r="H392" s="14"/>
-      <c r="I392" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J392" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K392" s="16"/>
-      <c r="L392" s="16"/>
-      <c r="M392" s="16"/>
-      <c r="N392" s="17"/>
-    </row>
-    <row r="393" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A393" s="13"/>
-      <c r="B393" s="14"/>
-      <c r="C393" s="14"/>
-      <c r="D393" s="14"/>
-      <c r="E393" s="14"/>
-      <c r="F393" s="14"/>
-      <c r="G393" s="14"/>
-      <c r="H393" s="14"/>
-      <c r="I393" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J393" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K393" s="16"/>
-      <c r="L393" s="16"/>
-      <c r="M393" s="16"/>
-      <c r="N393" s="17"/>
-    </row>
-    <row r="394" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A394" s="13"/>
-      <c r="B394" s="14"/>
-      <c r="C394" s="14"/>
-      <c r="D394" s="14"/>
-      <c r="E394" s="14"/>
-      <c r="F394" s="14"/>
-      <c r="G394" s="14"/>
-      <c r="H394" s="14"/>
-      <c r="I394" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J394" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K394" s="16"/>
-      <c r="L394" s="16"/>
-      <c r="M394" s="16"/>
-      <c r="N394" s="17"/>
-    </row>
-    <row r="395" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A395" s="13"/>
-      <c r="B395" s="14"/>
-      <c r="C395" s="14"/>
-      <c r="D395" s="14"/>
-      <c r="E395" s="14"/>
-      <c r="F395" s="14"/>
-      <c r="G395" s="14"/>
-      <c r="H395" s="14"/>
-      <c r="I395" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J395" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K395" s="16"/>
-      <c r="L395" s="16"/>
-      <c r="M395" s="16"/>
-      <c r="N395" s="17"/>
-    </row>
-    <row r="396" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A396" s="13"/>
-      <c r="B396" s="14"/>
-      <c r="C396" s="14"/>
-      <c r="D396" s="14"/>
-      <c r="E396" s="14"/>
-      <c r="F396" s="14"/>
-      <c r="G396" s="14"/>
-      <c r="H396" s="14"/>
-      <c r="I396" s="15" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="J396" s="15" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="K396" s="16"/>
-      <c r="L396" s="16"/>
-      <c r="M396" s="16"/>
-      <c r="N396" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -10202,7 +8571,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J24:J396 J6 J8:J12">
+  <conditionalFormatting sqref="J6 J8:J12 J24:J321">
     <cfRule type="cellIs" dxfId="2" priority="4" operator="lessThan">
       <formula>0</formula>
     </cfRule>
@@ -10218,15 +8587,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K396">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K321">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L396">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L321">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M396">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M321">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>
